--- a/reports/telegram/aegis_india_2026-09-04.xlsx
+++ b/reports/telegram/aegis_india_2026-09-04.xlsx
@@ -484,13 +484,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS INVESTMENTS · daily operator view · NEW opportunities + ACTIVE holdings across all runners · Dynamic Stop mandatory · R1 rows tagged SUGGESTED (no auto-exit per V2 §18)</t>
+          <t>AEGIS INVESTMENTS · daily operator view · NEW opportunities + ACTIVE holdings across all runners · Dynamic Stop mandatory · R1 rows tagged SUGGESTED · ⚠ R1 POSITIONS CARRY NO DYNAMIC-EXIT PROTECTION · advisory only · no auto-exit enforcement (per AEGIS Master v2 §R1.9 Stage 1 requirement)</t>
         </is>
       </c>
     </row>
@@ -613,34 +613,34 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1426.5</v>
+        <v>1430</v>
       </c>
       <c r="H5" t="n">
-        <v>1426.5</v>
+        <v>1430</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1395.0143 · SUGGESTED</t>
+          <t>1399.2571 · SUGGESTED</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1473.7286</v>
+        <v>1476.1143</v>
       </c>
       <c r="M5" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="N5" t="n">
         <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.2%) • outperforming Ni</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.4%) • outperforming Ni</t>
         </is>
       </c>
     </row>
@@ -674,40 +674,40 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1931.699951171875</v>
+        <v>1916</v>
       </c>
       <c r="H6" t="n">
-        <v>1931.699951171875</v>
+        <v>1916</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1873.9571 · SUGGESTED</t>
+          <t>1859.0429 · SUGGESTED</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2018.3142</v>
+        <v>2001.4357</v>
       </c>
       <c r="M6" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="N6" t="n">
         <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low-risk Pharma holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty </t>
+          <t xml:space="preserve">Low-risk Pharma holding (low vol) • above 200-dma (+6.4%) • outperforming Nifty </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -735,40 +735,40 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>330</v>
+        <v>330.8999938964844</v>
       </c>
       <c r="H7" t="n">
-        <v>330</v>
+        <v>330.8999938964844</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>319.5429 · SUGGESTED</t>
+          <t>320.8071 · SUGGESTED</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>345.6857</v>
+        <v>346.0393</v>
       </c>
       <c r="M7" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
         <v>1.5</v>
       </c>
       <c r="O7" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-7.6%) • sector strength 36/10</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.4%) • sector strength 8/100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -777,12 +777,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,40 +796,40 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1020.900024414062</v>
+        <v>265.6000061035156</v>
       </c>
       <c r="H8" t="n">
-        <v>1020.900024414062</v>
+        <v>265.6000061035156</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>993.0286 · SUGGESTED</t>
+          <t>256.7071 · SUGGESTED</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1062.7072</v>
+        <v>278.9393</v>
       </c>
       <c r="M8" t="n">
-        <v>2.73</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
         <v>1.5</v>
       </c>
       <c r="O8" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.7%) • outperforming Ni</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.6%) • sector strength 8/100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -838,12 +838,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -857,40 +857,40 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>266.7999877929688</v>
+        <v>236</v>
       </c>
       <c r="H9" t="n">
-        <v>266.7999877929688</v>
+        <v>236</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>258.1143 · SUGGESTED</t>
+          <t>229.9143 · SUGGESTED</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>279.8286</v>
+        <v>245.1286</v>
       </c>
       <c r="M9" t="n">
-        <v>3.26</v>
+        <v>2.58</v>
       </c>
       <c r="N9" t="n">
         <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.2%) • sector strength 36/10</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.4%) • sector strength 54/1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -899,12 +899,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -918,190 +918,195 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>237.5</v>
+        <v>408.6000061035156</v>
       </c>
       <c r="H10" t="n">
-        <v>237.5</v>
+        <v>408.6000061035156</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>231.1928 · SUGGESTED</t>
+          <t>397.6 · SUGGESTED</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>246.9607</v>
+        <v>425.1</v>
       </c>
       <c r="M10" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="N10" t="n">
         <v>1.5</v>
       </c>
       <c r="O10" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.8%) • sector strength 57/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>76</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BUY · R1 ADVISORY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>405.75</v>
-      </c>
-      <c r="H11" t="n">
-        <v>405.75</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>394.5143 · SUGGESTED</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>422.6036</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>66</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.2%) • sector strength</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.5%) • sector strength</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>🟡 ACTIVE POSITIONS · currently held · sorted by Score ↓</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>🟡 ACTIVE POSITIONS · currently held · sorted by Score ↓</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Runner</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Entry Date</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Entry Price</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Current Price</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Unrealized P&amp;L %</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Dynamic Stop</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Stop Distance %</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>R:R</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>Confidence %</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Reason</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Runner</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Entry Date</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Entry Price</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Current Price</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Unrealized P&amp;L %</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>Holding Days</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>Dynamic Stop</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Stop Distance %</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>R:R</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>Confidence %</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>Reason</t>
+      <c r="A15" t="n">
+        <v>55</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>587.35</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>530.3857</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>587.6713999999999</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>R2 · 6-03d0a7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1132,10 +1137,10 @@
         <v>397</v>
       </c>
       <c r="H16" t="n">
-        <v>425</v>
+        <v>421.15</v>
       </c>
       <c r="I16" t="n">
-        <v>7.05</v>
+        <v>6.08</v>
       </c>
       <c r="J16" t="n">
         <v>31</v>
@@ -1149,7 +1154,7 @@
         <v>412.8143</v>
       </c>
       <c r="M16" t="n">
-        <v>9.07</v>
+        <v>8.24</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1164,7 +1169,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1173,12 +1178,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1192,30 +1197,30 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H17" t="n">
-        <v>408.25</v>
+        <v>5657</v>
       </c>
       <c r="I17" t="n">
-        <v>4.33</v>
+        <v>2.87</v>
       </c>
       <c r="J17" t="n">
         <v>30</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>373.5786</t>
+          <t>5195.5001</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>417.8821</v>
+        <v>5954.2499</v>
       </c>
       <c r="M17" t="n">
-        <v>8.49</v>
+        <v>8.16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.28</v>
+        <v>0.64</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1224,13 +1229,13 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>R2 · 5-035a2d</t>
+          <t>R2 · 5-fc13a0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1239,12 +1244,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1254,34 +1259,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H18" t="n">
-        <v>5690</v>
+        <v>116.32</v>
       </c>
       <c r="I18" t="n">
-        <v>3.47</v>
+        <v>2.61</v>
       </c>
       <c r="J18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>5195.5001</t>
+          <t>109.6843</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5954.2499</v>
+        <v>118.8736</v>
       </c>
       <c r="M18" t="n">
-        <v>8.69</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1290,13 +1295,13 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>R2 · 5-fc13a0</t>
+          <t>R2 · 4-ffee9e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1305,12 +1310,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1320,34 +1325,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>553.3</v>
+        <v>2744.3</v>
       </c>
       <c r="H19" t="n">
-        <v>576.95</v>
+        <v>2735.3999</v>
       </c>
       <c r="I19" t="n">
-        <v>4.27</v>
+        <v>-0.32</v>
       </c>
       <c r="J19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>530.3857</t>
+          <t>2607.1858</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>587.6713999999999</v>
+        <v>2949.9715</v>
       </c>
       <c r="M19" t="n">
-        <v>8.07</v>
+        <v>4.69</v>
       </c>
       <c r="N19" t="n">
-        <v>0.23</v>
+        <v>1.67</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1356,64 +1361,64 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>R2 · 6-03d0a7</t>
+          <t>R2 · 5-7e40ba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>HOLD · R1 ADVISORY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>113.36</v>
+        <v>417.6</v>
       </c>
       <c r="H20" t="n">
-        <v>117</v>
+        <v>420.05</v>
       </c>
       <c r="I20" t="n">
-        <v>3.21</v>
+        <v>0.59</v>
       </c>
       <c r="J20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>109.6843</t>
+          <t>407.3714 · SUGGESTED</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>118.8736</v>
+        <v>432.9429</v>
       </c>
       <c r="M20" t="n">
-        <v>6.25</v>
+        <v>3.02</v>
       </c>
       <c r="N20" t="n">
-        <v>0.26</v>
+        <v>1.02</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1422,64 +1427,64 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>R2 · 4-ffee9e</t>
+          <t>R1 ADVISORY · 5-9349c5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>HOLD · R1 ADVISORY</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2744.3</v>
+        <v>1642.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2720</v>
+        <v>1638.3</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.89</v>
+        <v>-0.26</v>
       </c>
       <c r="J21" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2607.1858</t>
+          <t>1594.6857 · SUGGESTED</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2949.9715</v>
+        <v>1714.2215</v>
       </c>
       <c r="M21" t="n">
-        <v>4.15</v>
+        <v>2.66</v>
       </c>
       <c r="N21" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1488,13 +1493,13 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>R2 · 5-7e40ba</t>
+          <t>R1 ADVISORY · 4-cf5c6a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1525,10 +1530,10 @@
         <v>1413.5</v>
       </c>
       <c r="H22" t="n">
-        <v>1423</v>
+        <v>1412.8</v>
       </c>
       <c r="I22" t="n">
-        <v>0.67</v>
+        <v>-0.05</v>
       </c>
       <c r="J22" t="n">
         <v>7</v>
@@ -1542,10 +1547,10 @@
         <v>1460.1715</v>
       </c>
       <c r="M22" t="n">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="N22" t="n">
-        <v>0.92</v>
+        <v>1.56</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1560,7 +1565,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1569,7 +1574,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1584,34 +1589,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1642.5</v>
+        <v>187.46</v>
       </c>
       <c r="H23" t="n">
-        <v>1643.5</v>
+        <v>184.2</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06</v>
+        <v>-1.74</v>
       </c>
       <c r="J23" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1594.6857 · SUGGESTED</t>
+          <t>181.8114 · SUGGESTED</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1714.2215</v>
+        <v>195.9329</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>1.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.45</v>
+        <v>4.91</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1620,13 +1625,13 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 4-cf5c6a</t>
+          <t>R1 ADVISORY · 8-c215bb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1635,12 +1640,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1650,34 +1655,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>417.6</v>
+        <v>385.15</v>
       </c>
       <c r="H24" t="n">
-        <v>417.85</v>
+        <v>380.7</v>
       </c>
       <c r="I24" t="n">
-        <v>0.06</v>
+        <v>-1.16</v>
       </c>
       <c r="J24" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>407.3714 · SUGGESTED</t>
+          <t>377.5071 · SUGGESTED</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>432.9429</v>
+        <v>396.6143</v>
       </c>
       <c r="M24" t="n">
-        <v>2.51</v>
+        <v>0.84</v>
       </c>
       <c r="N24" t="n">
-        <v>1.44</v>
+        <v>4.98</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1686,22 +1691,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 5-9349c5</t>
+          <t>R1 ADVISORY · 8-be7819</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>HOLD · R1 ADVISORY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1711,39 +1716,39 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>11475</v>
+        <v>1048.7</v>
       </c>
       <c r="H25" t="n">
-        <v>11310</v>
+        <v>1023.4</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.44</v>
+        <v>-2.41</v>
       </c>
       <c r="J25" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11144.7143</t>
+          <t>1011.5999 · SUGGESTED</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>11970.4286</v>
+        <v>1104.35</v>
       </c>
       <c r="M25" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>6.86</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1752,64 +1757,61 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>R2 · 5-b3d435</t>
+          <t>R1 ADVISORY · 1-b637f4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HOLD · R1 ADVISORY</t>
+          <t>EXIT · stop hit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1191</v>
+        <v>11475</v>
       </c>
       <c r="H26" t="n">
-        <v>1167.8</v>
+        <v>11100</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.95</v>
+        <v>-3.27</v>
       </c>
       <c r="J26" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1149.2286 · SUGGESTED</t>
+          <t>11144.7143</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1253.6571</v>
+        <v>11970.4286</v>
       </c>
       <c r="M26" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.62</v>
+        <v>-0.4</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1818,64 +1820,61 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 1-58636b</t>
+          <t>R2 · 5-b3d435</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HOLD · R1 ADVISORY</t>
+          <t>EXIT · stop hit</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>187.46</v>
+        <v>709</v>
       </c>
       <c r="H27" t="n">
-        <v>183.85</v>
+        <v>677.4</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.93</v>
+        <v>-4.46</v>
       </c>
       <c r="J27" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>181.8114 · SUGGESTED</t>
+          <t>682.2286</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>195.9329</v>
+        <v>749.1571</v>
       </c>
       <c r="M27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5.93</v>
+        <v>-0.71</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -1884,13 +1883,13 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 8-c215bb</t>
+          <t>R2 · 4-a68e4b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1899,12 +1898,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1914,34 +1913,31 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>385.15</v>
+        <v>381.6</v>
       </c>
       <c r="H28" t="n">
-        <v>379</v>
+        <v>365.7</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.6</v>
+        <v>-4.17</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>377.5071 · SUGGESTED</t>
+          <t>369.75 · SUGGESTED</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>396.6143</v>
+        <v>399.375</v>
       </c>
       <c r="M28" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="N28" t="n">
-        <v>11.8</v>
+        <v>-1.11</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -1950,7 +1946,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 8-be7819</t>
+          <t>R1 ADVISORY · 4-29907f</t>
         </is>
       </c>
     </row>
@@ -1965,12 +1961,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1980,31 +1976,31 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2064.8999</v>
+        <v>1191</v>
       </c>
       <c r="H29" t="n">
-        <v>1975</v>
+        <v>1143</v>
       </c>
       <c r="I29" t="n">
-        <v>-4.35</v>
+        <v>-4.03</v>
       </c>
       <c r="J29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1990.457 · SUGGESTED</t>
+          <t>1149.2286 · SUGGESTED</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2176.5643</v>
+        <v>1253.6571</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.78</v>
+        <v>-0.54</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2013,7 +2009,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 2-08d1f5</t>
+          <t>R1 ADVISORY · 1-58636b</t>
         </is>
       </c>
     </row>
@@ -2023,51 +2019,51 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EXIT · stop hit</t>
+          <t>HOLD · R1 ADVISORY</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>709</v>
+        <v>2064.8999</v>
       </c>
       <c r="H30" t="n">
-        <v>670.45</v>
+        <v>1962</v>
       </c>
       <c r="I30" t="n">
-        <v>-5.44</v>
+        <v>-4.98</v>
       </c>
       <c r="J30" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>682.2286</t>
+          <t>1990.457 · SUGGESTED</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>749.1571</v>
+        <v>2176.5643</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.76</v>
+        <v>-1.45</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2076,13 +2072,13 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>R2 · 4-a68e4b</t>
+          <t>R1 ADVISORY · 2-08d1f5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2091,12 +2087,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2110,27 +2106,27 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>381.6</v>
+        <v>5454.5</v>
       </c>
       <c r="H31" t="n">
-        <v>364</v>
+        <v>5130</v>
       </c>
       <c r="I31" t="n">
-        <v>-4.61</v>
+        <v>-5.95</v>
       </c>
       <c r="J31" t="n">
         <v>31</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>369.75 · SUGGESTED</t>
+          <t>5283.7143 · SUGGESTED</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>399.375</v>
+        <v>5710.6786</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.58</v>
+        <v>-3</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2139,13 +2135,13 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 4-29907f</t>
+          <t>R1 ADVISORY · 4-3de31c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2154,12 +2150,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2173,27 +2169,27 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>5454.5</v>
+        <v>507.9</v>
       </c>
       <c r="H32" t="n">
-        <v>5154</v>
+        <v>474.6</v>
       </c>
       <c r="I32" t="n">
-        <v>-5.51</v>
+        <v>-6.56</v>
       </c>
       <c r="J32" t="n">
         <v>31</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>5283.7143 · SUGGESTED</t>
+          <t>493.3286 · SUGGESTED</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5710.6786</v>
+        <v>529.7572</v>
       </c>
       <c r="M32" t="n">
-        <v>-2.52</v>
+        <v>-3.95</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2202,13 +2198,13 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 4-3de31c</t>
+          <t>R1 ADVISORY · 4-afbb8f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2217,12 +2213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2236,27 +2232,27 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>284.85</v>
+        <v>452.35</v>
       </c>
       <c r="H33" t="n">
-        <v>266.3</v>
+        <v>418.3</v>
       </c>
       <c r="I33" t="n">
-        <v>-6.51</v>
+        <v>-7.53</v>
       </c>
       <c r="J33" t="n">
         <v>31</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>276.1</t>
+          <t>435.5929</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>297.975</v>
+        <v>477.4857</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.68</v>
+        <v>-4.13</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2265,32 +2261,32 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>R2 · 4-e0ebbb</t>
+          <t>R2 · 4-893fdf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HOLD · R1 ADVISORY</t>
+          <t>EXIT · stop hit</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2299,27 +2295,27 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>507.9</v>
+        <v>284.85</v>
       </c>
       <c r="H34" t="n">
-        <v>472.6</v>
+        <v>263</v>
       </c>
       <c r="I34" t="n">
-        <v>-6.95</v>
+        <v>-7.67</v>
       </c>
       <c r="J34" t="n">
         <v>31</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>493.3286 · SUGGESTED</t>
+          <t>276.1</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>529.7572</v>
+        <v>297.975</v>
       </c>
       <c r="M34" t="n">
-        <v>-4.39</v>
+        <v>-4.98</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2328,61 +2324,61 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · 4-afbb8f</t>
+          <t>R2 · 4-e0ebbb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXIT · stop hit</t>
+          <t>HOLD · R1 ADVISORY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>452.35</v>
+        <v>2410</v>
       </c>
       <c r="H35" t="n">
-        <v>412.3</v>
+        <v>2132</v>
       </c>
       <c r="I35" t="n">
-        <v>-8.85</v>
+        <v>-11.54</v>
       </c>
       <c r="J35" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>435.5929</t>
+          <t>2314.8285 · SUGGESTED</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>477.4857</v>
+        <v>2552.7572</v>
       </c>
       <c r="M35" t="n">
-        <v>-5.65</v>
+        <v>-8.58</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2391,153 +2387,89 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>R2 · 4-893fdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>14</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>HOLD · R1 ADVISORY</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>2410</v>
-      </c>
-      <c r="H36" t="n">
-        <v>2153</v>
-      </c>
-      <c r="I36" t="n">
-        <v>-10.66</v>
-      </c>
-      <c r="J36" t="n">
-        <v>30</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>2314.8285 · SUGGESTED</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>2552.7572</v>
-      </c>
-      <c r="M36" t="n">
-        <v>-7.52</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
           <t>R1 ADVISORY · 5-71abab</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Score · unified 0-100 · higher = better · combines confidence + P&amp;L trend + safety margin</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Score · unified 0-100 · higher = better · combines confidence + P&amp;L trend + safety margin</t>
+          <t>Action · BUY (new) · HOLD (active above stop) · EXIT (stop hit) · REVIEW (data error)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Action · BUY (new) · HOLD (active above stop) · EXIT (stop hit) · REVIEW (data error)</t>
+          <t>Runner · which engine produced the signal · R1=advisory · R2=production · Composite=research</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Runner · which engine produced the signal · R1=advisory · R2=production · Composite=research</t>
+          <t>Dynamic Stop · MANDATORY on every row · trichotomy:</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Stop · MANDATORY on every row · trichotomy:</t>
+          <t xml:space="preserve">  ₹XXX                        = valid dynamic stop (R2 · ATR-14 · k=2)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ₹XXX                        = valid dynamic stop (R2 · ATR-14 · k=2)</t>
+          <t xml:space="preserve">  ₹XXX · SUGGESTED           = R1 advisory · no auto-exit per V2 §18</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ₹XXX · SUGGESTED           = R1 advisory · no auto-exit per V2 §18</t>
+          <t xml:space="preserve">  N/A · advisory · no auto-exit = R1 with no ATR available</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  N/A · advisory · no auto-exit = R1 with no ATR available</t>
+          <t xml:space="preserve">  DATA_ERROR · &lt;reason&gt;       = engine/data failure · never blank</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DATA_ERROR · &lt;reason&gt;       = engine/data failure · never blank</t>
+          <t>Entry Date · from Registry for active positions · today for new BUY</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Entry Date · from Registry for active positions · today for new BUY</t>
+          <t>Holding Days · active positions only · calendar days since Registry entry</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Holding Days · active positions only · calendar days since Registry entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
           <t>R:R · Reward/Risk · (Target − Current) / (Current − Stop) · only when both present</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A49:P49"/>
     <mergeCell ref="A47:P47"/>
     <mergeCell ref="A42:P42"/>
     <mergeCell ref="A46:P46"/>
@@ -2547,6 +2479,7 @@
     <mergeCell ref="A45:P45"/>
     <mergeCell ref="A39:P39"/>
     <mergeCell ref="A48:P48"/>
+    <mergeCell ref="A38:P38"/>
     <mergeCell ref="A43:P43"/>
     <mergeCell ref="A41:P41"/>
   </mergeCells>
@@ -2943,7 +2876,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2971,7 +2904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3006,7 +2939,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>🟢 R2 ACTIVE: 9 · production runner is R2 · sorted latest entry first · rebuilt daily from canonical Registry</t>
+          <t>🟢 R2 ACTIVE: 8 · production runner is R2 · sorted latest entry first · rebuilt daily from canonical Registry</t>
         </is>
       </c>
     </row>
@@ -3142,10 +3075,10 @@
         <v>553.3</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>576.95</v>
+        <v>587.35</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>4.27</v>
+        <v>6.15</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>29</v>
@@ -3169,7 +3102,7 @@
         <v>587.6713999999999</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1.86</v>
+        <v>0.05</v>
       </c>
       <c r="O5" s="6" t="n">
         <v>60</v>
@@ -3230,10 +3163,10 @@
         <v>11475</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>11310</v>
+        <v>11100</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-1.44</v>
+        <v>-3.27</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>30</v>
@@ -3257,7 +3190,7 @@
         <v>11970.4286</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>5.84</v>
+        <v>7.84</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>60</v>
@@ -3291,17 +3224,17 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -3315,13 +3248,13 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>408.25</v>
+        <v>5657</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>4.33</v>
+        <v>2.87</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>30</v>
@@ -3342,10 +3275,10 @@
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>417.8821</v>
+        <v>5954.2499</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>2.36</v>
+        <v>5.25</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>60</v>
@@ -3379,17 +3312,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -3403,13 +3336,13 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>5499</v>
+        <v>2744.3</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>5690</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>3.47</v>
+        <v>2735.3999</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>-0.32</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>30</v>
@@ -3430,10 +3363,10 @@
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>5954.2499</v>
+        <v>2949.9715</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>4.64</v>
+        <v>7.84</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>60</v>
@@ -3467,17 +3400,17 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -3487,20 +3420,20 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2744.3</v>
+        <v>709</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2720</v>
+        <v>677.4</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-0.89</v>
+        <v>-4.46</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -3518,10 +3451,10 @@
         </is>
       </c>
       <c r="M9" s="6" t="n">
-        <v>2949.9715</v>
+        <v>749.1571</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>8.449999999999999</v>
+        <v>10.59</v>
       </c>
       <c r="O9" s="6" t="n">
         <v>60</v>
@@ -3538,7 +3471,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04 (~30d)</t>
+          <t>2026-10-03 (~29d)</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -3555,17 +3488,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -3579,13 +3512,13 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>709</v>
+        <v>452.35</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>670.45</v>
+        <v>418.3</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-5.44</v>
+        <v>-7.53</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>31</v>
@@ -3606,10 +3539,10 @@
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>749.1571</v>
+        <v>477.4857</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>11.74</v>
+        <v>14.15</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>60</v>
@@ -3643,17 +3576,17 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
+          <t>IND-R2-ITC-20260804-e0ebbb</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -3667,13 +3600,13 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>452.35</v>
+        <v>284.85</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>412.3</v>
+        <v>263</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>-8.85</v>
+        <v>-7.67</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>31</v>
@@ -3694,10 +3627,10 @@
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>477.4857</v>
+        <v>297.975</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>15.81</v>
+        <v>13.3</v>
       </c>
       <c r="O11" s="6" t="n">
         <v>60</v>
@@ -3731,17 +3664,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ITC-20260804-e0ebbb</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -3755,13 +3688,13 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>284.85</v>
+        <v>113.36</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>266.3</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>-6.51</v>
+        <v>116.32</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>2.61</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>31</v>
@@ -3782,10 +3715,10 @@
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>297.975</v>
+        <v>118.8736</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>11.89</v>
+        <v>2.2</v>
       </c>
       <c r="O12" s="6" t="n">
         <v>60</v>
@@ -3816,166 +3749,78 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>113.36</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>117</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>118.8736</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O13" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE · no canonical stop</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-03 (~29d)</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr">
-        <is>
-          <t>canonical:Registry+dynamic_risk_v2+prices+sector_cache+target_src=atr_fallback_m3</t>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>This sheet shows CURRENT R2 active holdings ONLY. Closed positions live in 03_Exit_History.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>This sheet shows CURRENT R2 active holdings ONLY. Closed positions live in 03_Exit_History.</t>
+          <t>Unrealized P&amp;L % · (Current − Entry) / Entry · positive=green · negative=red.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Unrealized P&amp;L % · (Current − Entry) / Entry · positive=green · negative=red.</t>
+          <t>Dynamic Stop · canonical dynamic_risk_v2 output · authoritative production value.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Stop · canonical dynamic_risk_v2 output · authoritative production value.</t>
+          <t>Stop Distance % · (Current − Stop) / Current · numeric so operator can sort by risk buffer.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Stop Distance % · (Current − Stop) / Current · numeric so operator can sort by risk buffer.</t>
+          <t>Target · Registry-provided OR ATR-based fallback = Entry + 3·ATR14(entry) · same math as P0 replay · Provenance shows source.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Target · Registry-provided OR ATR-based fallback = Entry + 3·ATR14(entry) · same math as P0 replay · Provenance shows source.</t>
+          <t>Target Distance % · (Target − Current) / Current · shows upside gap.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Target Distance % · (Target − Current) / Current · shows upside gap.</t>
+          <t>Exit Horizon · days from Registry initial_signal · defaults to 60 (P0 horizon) when source has no horizon.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Exit Horizon · days from Registry initial_signal · defaults to 60 (P0 horizon) when source has no horizon.</t>
+          <t>Est. Exit Window · FORWARD-LOOKING · entry_date + horizon · shows the planned close date + days-remaining.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Est. Exit Window · FORWARD-LOOKING · entry_date + horizon · shows the planned close date + days-remaining.</t>
+          <t>Risk/Reward · Reward / Risk = (Target−Current) / (Current−Stop) · only when both Target and Stop present.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Risk/Reward · Reward / Risk = (Target−Current) / (Current−Stop) · only when both Target and Stop present.</t>
+          <t>Action · HOLD (above stop) · EXIT (at/below stop) · REVIEW (no canonical stop available).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Action · HOLD (above stop) · EXIT (at/below stop) · REVIEW (no canonical stop available).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>UNAVAILABLE = canonical source returned no value · never fabricated.</t>
         </is>
@@ -3988,8 +3833,8 @@
     <mergeCell ref="A22:T22"/>
     <mergeCell ref="A17:T17"/>
     <mergeCell ref="A18:T18"/>
-    <mergeCell ref="A26:T26"/>
     <mergeCell ref="A21:T21"/>
+    <mergeCell ref="A15:T15"/>
     <mergeCell ref="A25:T25"/>
     <mergeCell ref="A20:T20"/>
     <mergeCell ref="A24:T24"/>
@@ -4208,7 +4053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4237,7 +4082,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>📕 This sheet · 20 realized production exits (last 90d) · newest first · realized P&amp;L only</t>
+          <t>📕 This sheet · 21 realized production exits (last 90d) · newest first · realized P&amp;L only</t>
         </is>
       </c>
     </row>
@@ -4323,17 +4168,17 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LUPIN-20260804-def33a</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4348,25 +4193,25 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>2383.8999</v>
+        <v>391.3</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>2160.2</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>-9.380000000000001</v>
+        <v>416.9</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>6.54</v>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
@@ -4374,7 +4219,7 @@
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>13</v>
+        <v>17.1</v>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
@@ -4385,17 +4230,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -4415,20 +4260,20 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H6" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>415.15</v>
+        <v>2383.8999</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>402.55</v>
+        <v>2160.2</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>-3.04</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
@@ -4436,7 +4281,7 @@
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>14.3</v>
+        <v>13</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
@@ -4447,17 +4292,17 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -4477,28 +4322,28 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>552.4</v>
+        <v>415.15</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>558</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>1.01</v>
+        <v>402.55</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>-3.04</v>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>Outperformance exit</t>
+          <t>Rotation swap</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
@@ -4509,17 +4354,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -4534,7 +4379,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -4543,16 +4388,16 @@
         </is>
       </c>
       <c r="H8" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>129.2</v>
+        <v>552.4</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>124.4</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>-3.72</v>
+        <v>558</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>1.01</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
@@ -4560,7 +4405,7 @@
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>12.2</v>
+        <v>14.7</v>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
@@ -4571,17 +4416,17 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -4601,20 +4446,20 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1384</v>
+        <v>129.2</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>1327.6</v>
+        <v>124.4</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>-4.08</v>
+        <v>-3.72</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
@@ -4622,7 +4467,7 @@
         </is>
       </c>
       <c r="M9" s="6" t="n">
-        <v>56.7</v>
+        <v>12.2</v>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
@@ -4633,17 +4478,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4670,13 +4515,13 @@
         <v>12</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>377</v>
+        <v>1384</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>387.55</v>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>2.8</v>
+        <v>1327.6</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>-4.08</v>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
@@ -4684,7 +4529,7 @@
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
@@ -4695,17 +4540,17 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260805-f0f538</t>
+          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -4725,20 +4570,20 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>11600</v>
+        <v>377</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>11828</v>
+        <v>387.55</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
@@ -4746,7 +4591,7 @@
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
@@ -4757,12 +4602,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260804-a45359</t>
+          <t>IND-R2-OFSS-20260805-f0f538</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4782,7 +4627,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -4791,16 +4636,16 @@
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>2439.3999</v>
+        <v>11600</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>2361</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>-3.21</v>
+        <v>11828</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>1.97</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
@@ -4808,7 +4653,7 @@
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
@@ -4819,17 +4664,17 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
+          <t>IND-R2-TCS-20260804-a45359</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -4849,20 +4694,20 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>7454.5</v>
+        <v>2439.3999</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>7095</v>
+        <v>2361</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>-4.82</v>
+        <v>-3.21</v>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
@@ -4870,7 +4715,7 @@
         </is>
       </c>
       <c r="M13" s="6" t="n">
-        <v>62.1</v>
+        <v>6.7</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
@@ -4881,17 +4726,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -4906,25 +4751,25 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>6793.5</v>
+        <v>7454.5</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>6774</v>
+        <v>7095</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>-0.29</v>
+        <v>-4.82</v>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
@@ -4932,7 +4777,7 @@
         </is>
       </c>
       <c r="M14" s="6" t="n">
-        <v>8</v>
+        <v>62.1</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
@@ -4943,17 +4788,17 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -4968,7 +4813,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -4977,16 +4822,16 @@
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>471.2</v>
+        <v>6793.5</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>0.45</v>
+        <v>6774</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>-0.29</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
@@ -4994,7 +4839,7 @@
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>60.7</v>
+        <v>8</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
@@ -5005,17 +4850,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
+          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -5030,7 +4875,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -5039,16 +4884,16 @@
         </is>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>845</v>
+        <v>471.2</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>889.5</v>
+        <v>473.3</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>5.27</v>
+        <v>0.45</v>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
@@ -5056,7 +4901,7 @@
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>7.4</v>
+        <v>60.7</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
@@ -5067,17 +4912,17 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260805-6635e1</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -5104,13 +4949,13 @@
         <v>2</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>450</v>
+        <v>845</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>442.8</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>-1.6</v>
+        <v>889.5</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>5.27</v>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
@@ -5118,7 +4963,7 @@
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>10.3</v>
+        <v>7.4</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
@@ -5129,17 +4974,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PRESTIGE-20260805-488bde</t>
+          <t>IND-R2-OIL-20260805-6635e1</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -5166,13 +5011,13 @@
         <v>2</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1595</v>
+        <v>450</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1584.8</v>
+        <v>442.8</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>-0.64</v>
+        <v>-1.6</v>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
@@ -5180,7 +5025,7 @@
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>62.5</v>
+        <v>10.3</v>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
@@ -5191,17 +5036,17 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
+          <t>IND-R2-PRESTIGE-20260805-488bde</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -5228,13 +5073,13 @@
         <v>2</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1327.7</v>
+        <v>1595</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1285</v>
+        <v>1584.8</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>-3.22</v>
+        <v>-0.64</v>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
@@ -5242,7 +5087,7 @@
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>64.8</v>
+        <v>62.5</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
@@ -5253,12 +5098,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
+          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -5283,20 +5128,20 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>2195</v>
+        <v>1327.7</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2182</v>
+        <v>1285</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>-0.59</v>
+        <v>-3.22</v>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
@@ -5304,7 +5149,7 @@
         </is>
       </c>
       <c r="M20" s="6" t="n">
-        <v>59.7</v>
+        <v>64.8</v>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
@@ -5315,17 +5160,17 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
+          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -5340,7 +5185,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -5349,16 +5194,16 @@
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1363.6</v>
+        <v>2195</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1351.3</v>
+        <v>2182</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>-0.9</v>
+        <v>-0.59</v>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
@@ -5366,7 +5211,7 @@
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>7.8</v>
+        <v>59.7</v>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
@@ -5377,17 +5222,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
+          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -5414,13 +5259,13 @@
         <v>2</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>5470.5</v>
+        <v>1363.6</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>5651.5</v>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>3.31</v>
+        <v>1351.3</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>-0.9</v>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
@@ -5428,7 +5273,7 @@
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
@@ -5439,17 +5284,17 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260805-ea04e5</t>
+          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -5464,7 +5309,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -5473,16 +5318,16 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1167.5</v>
+        <v>5470.5</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1177</v>
+        <v>5651.5</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.31</v>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
@@ -5490,7 +5335,7 @@
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>11.7</v>
+        <v>10.6</v>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
@@ -5501,109 +5346,171 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>IND-R2-INFY-20260805-ea04e5</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1167.5</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>1177</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>IND-R2-VEDL-20260804-563905</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>VEDL</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H25" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I25" s="6" t="n">
         <v>268.5</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J25" s="6" t="n">
         <v>278.8</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K25" s="7" t="n">
         <v>3.84</v>
       </c>
-      <c r="L24" s="6" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>Outperformance exit</t>
         </is>
       </c>
-      <c r="M24" s="6" t="n">
+      <c r="M25" s="6" t="n">
         <v>11.6</v>
       </c>
-      <c r="N24" s="6" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Priced: 20 · Unpriced (data unavailable): 0 · unpriced rows show — for P&amp;L, never fabricated 0.</t>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Realized P&amp;L % · (Exit − Entry) / Entry · own-trade result · positive=green · negative=red.</t>
+          <t>Priced: 21 · Unpriced (data unavailable): 0 · unpriced rows show — for P&amp;L, never fabricated 0.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Relative Opportunity pp · alpha/rotation benefit vs the closed position (pp = percentage points) · this is NOT the trade's own P&amp;L · shown separately so it cannot be misread.</t>
+          <t>Realized P&amp;L % · (Exit − Entry) / Entry · own-trade result · positive=green · negative=red.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>18 same-day / zero-Δ administrative events + 5 retired-runner events filtered from this operator-facing view · they remain in the canonical Registry JSONL and orphan_audit sink for audit.</t>
+          <t>Relative Opportunity pp · alpha/rotation benefit vs the closed position (pp = percentage points) · this is NOT the trade's own P&amp;L · shown separately so it cannot be misread.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>18 same-day / zero-Δ administrative events + 5 retired-runner events filtered from this operator-facing view · they remain in the canonical Registry JSONL and orphan_audit sink for audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>This sheet contains ONLY realized production exits · 90-day rolling window.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A27:N27"/>
     <mergeCell ref="A31:N31"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A30:N30"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A29:N29"/>
     <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A32:N32"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5616,7 +5523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M331"/>
+  <dimension ref="A1:M330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6699,12 +6606,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -6723,10 +6630,10 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
@@ -6760,12 +6667,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -6780,17 +6687,17 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>5499</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>0</v>
+        <v>113.99</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -6821,12 +6728,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -6841,17 +6748,17 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G23" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>113.99</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>0.5600000000000001</v>
+        <v>2744.3</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -6882,12 +6789,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -6906,10 +6813,10 @@
         </is>
       </c>
       <c r="G24" s="6" t="n">
-        <v>2744.3</v>
+        <v>1384</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2744.3</v>
+        <v>1384</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
@@ -6943,12 +6850,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -6963,17 +6870,17 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1384</v>
+        <v>7454.5</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1384</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>7395</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>-0.8</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -7004,12 +6911,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -7024,17 +6931,17 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>7454.5</v>
+        <v>6793.5</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>7395</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>-0.8</v>
+        <v>6793.5</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
@@ -7065,12 +6972,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
+          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -7089,10 +6996,10 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>6793.5</v>
+        <v>2195</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>6793.5</v>
+        <v>2195</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
@@ -7126,12 +7033,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -7146,17 +7053,17 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>2195</v>
+        <v>415.15</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>2195</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>0</v>
+        <v>417.6</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0.59</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -7187,12 +7094,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -7211,13 +7118,13 @@
         </is>
       </c>
       <c r="G29" s="6" t="n">
-        <v>415.15</v>
+        <v>1363.6</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>417.6</v>
+        <v>1369.9</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -7248,12 +7155,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
+          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -7272,13 +7179,13 @@
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>1363.6</v>
+        <v>5470.5</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>1369.9</v>
+        <v>5548</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0.46</v>
+        <v>1.42</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -7309,12 +7216,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -7333,13 +7240,13 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>5470.5</v>
+        <v>552.4</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>5548</v>
+        <v>562.9</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -7370,12 +7277,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -7390,17 +7297,17 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>552.4</v>
+        <v>129.2</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>562.9</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>1.9</v>
+        <v>129.2</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -7431,12 +7338,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -7455,10 +7362,10 @@
         </is>
       </c>
       <c r="G33" s="6" t="n">
-        <v>129.2</v>
+        <v>845</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>129.2</v>
+        <v>845</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
@@ -7492,12 +7399,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
+          <t>IND-R2-INFY-20260805-ea04e5</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -7516,10 +7423,10 @@
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>845</v>
+        <v>1167.5</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>845</v>
+        <v>1167.5</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
@@ -7553,12 +7460,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260805-ea04e5</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -7577,10 +7484,10 @@
         </is>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1167.5</v>
+        <v>391.3</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1167.5</v>
+        <v>391.3</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
@@ -8407,12 +8314,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -8431,13 +8338,13 @@
         </is>
       </c>
       <c r="G49" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>387.9</v>
-      </c>
-      <c r="I49" s="8" t="n">
-        <v>-0.87</v>
+        <v>5532.5</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>0.61</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
@@ -8468,12 +8375,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -8488,17 +8395,17 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G50" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>5532.5</v>
+        <v>113.54</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>0.61</v>
+        <v>0.16</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -8529,12 +8436,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -8549,17 +8456,17 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G51" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>113.54</v>
+        <v>2764.2</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>0.16</v>
+        <v>0.73</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -8590,12 +8497,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -8614,13 +8521,13 @@
         </is>
       </c>
       <c r="G52" s="6" t="n">
-        <v>2744.3</v>
+        <v>1384</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>2764.2</v>
-      </c>
-      <c r="I52" s="7" t="n">
-        <v>0.73</v>
+        <v>1378.5</v>
+      </c>
+      <c r="I52" s="8" t="n">
+        <v>-0.4</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
@@ -8651,12 +8558,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -8671,17 +8578,17 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G53" s="6" t="n">
-        <v>1384</v>
+        <v>7454.5</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>1378.5</v>
-      </c>
-      <c r="I53" s="8" t="n">
-        <v>-0.4</v>
+        <v>7531.5</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>1.03</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -8712,12 +8619,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -8732,17 +8639,17 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
-        <v>7454.5</v>
+        <v>6793.5</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>7531.5</v>
+        <v>6834</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>1.03</v>
+        <v>0.6</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -8773,12 +8680,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -8793,17 +8700,17 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
-        <v>6793.5</v>
+        <v>415.15</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>6834</v>
-      </c>
-      <c r="I55" s="7" t="n">
-        <v>0.6</v>
+        <v>414.05</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>-0.26</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -8834,12 +8741,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -8854,17 +8761,17 @@
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G56" s="6" t="n">
-        <v>415.15</v>
+        <v>471.2</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>414.05</v>
-      </c>
-      <c r="I56" s="8" t="n">
-        <v>-0.26</v>
+        <v>471.2</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -8895,12 +8802,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -8915,17 +8822,17 @@
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G57" s="6" t="n">
-        <v>471.2</v>
+        <v>552.4</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>471.2</v>
-      </c>
-      <c r="I57" s="6" t="n">
-        <v>0</v>
+        <v>597.55</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>8.17</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -8956,12 +8863,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -8976,17 +8883,17 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G58" s="6" t="n">
-        <v>552.4</v>
+        <v>129.2</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>597.55</v>
+        <v>129.61</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>8.17</v>
+        <v>0.32</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -9017,12 +8924,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -9041,13 +8948,13 @@
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>129.2</v>
+        <v>845</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>129.61</v>
+        <v>853.4</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>0.32</v>
+        <v>0.99</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -9078,12 +8985,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -9102,13 +9009,13 @@
         </is>
       </c>
       <c r="G60" s="6" t="n">
-        <v>845</v>
+        <v>391.3</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>853.4</v>
-      </c>
-      <c r="I60" s="7" t="n">
-        <v>0.99</v>
+        <v>387.9</v>
+      </c>
+      <c r="I60" s="8" t="n">
+        <v>-0.87</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -9871,12 +9778,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -9895,13 +9802,13 @@
         </is>
       </c>
       <c r="G73" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>394</v>
-      </c>
-      <c r="I73" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>5475</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>-0.44</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
@@ -9932,12 +9839,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -9952,17 +9859,17 @@
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>5475</v>
-      </c>
-      <c r="I74" s="8" t="n">
-        <v>-0.44</v>
+        <v>114.81</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>1.28</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -9993,12 +9900,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -10013,17 +9920,17 @@
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G75" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>114.81</v>
+        <v>2772</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -10054,12 +9961,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -10078,13 +9985,13 @@
         </is>
       </c>
       <c r="G76" s="6" t="n">
-        <v>2744.3</v>
+        <v>1384</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>2772</v>
-      </c>
-      <c r="I76" s="7" t="n">
-        <v>1.01</v>
+        <v>1372.4</v>
+      </c>
+      <c r="I76" s="8" t="n">
+        <v>-0.84</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
@@ -10115,12 +10022,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -10135,17 +10042,17 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G77" s="6" t="n">
-        <v>1384</v>
+        <v>7454.5</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>1372.4</v>
+        <v>7435</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>-0.84</v>
+        <v>-0.26</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -10176,12 +10083,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -10200,13 +10107,13 @@
         </is>
       </c>
       <c r="G78" s="6" t="n">
-        <v>7454.5</v>
+        <v>415.15</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>7435</v>
-      </c>
-      <c r="I78" s="8" t="n">
-        <v>-0.26</v>
+        <v>415.25</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>0.02</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -10237,12 +10144,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -10261,13 +10168,13 @@
         </is>
       </c>
       <c r="G79" s="6" t="n">
-        <v>415.15</v>
+        <v>552.4</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>415.25</v>
+        <v>603</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>0.02</v>
+        <v>9.16</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -10298,12 +10205,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -10318,17 +10225,17 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G80" s="6" t="n">
-        <v>552.4</v>
+        <v>129.2</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>603</v>
-      </c>
-      <c r="I80" s="7" t="n">
-        <v>9.16</v>
+        <v>127.1</v>
+      </c>
+      <c r="I80" s="8" t="n">
+        <v>-1.63</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
@@ -10359,12 +10266,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -10383,13 +10290,13 @@
         </is>
       </c>
       <c r="G81" s="6" t="n">
-        <v>129.2</v>
+        <v>391.3</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>127.1</v>
-      </c>
-      <c r="I81" s="8" t="n">
-        <v>-1.63</v>
+        <v>394</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -10969,12 +10876,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -10993,13 +10900,13 @@
         </is>
       </c>
       <c r="G91" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>393</v>
-      </c>
-      <c r="I91" s="7" t="n">
-        <v>0.43</v>
+        <v>5474</v>
+      </c>
+      <c r="I91" s="8" t="n">
+        <v>-0.45</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -11030,12 +10937,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -11050,17 +10957,17 @@
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G92" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>5474</v>
-      </c>
-      <c r="I92" s="8" t="n">
-        <v>-0.45</v>
+        <v>113.5</v>
+      </c>
+      <c r="I92" s="7" t="n">
+        <v>0.12</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -11091,12 +10998,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -11111,17 +11018,17 @@
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G93" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>113.5</v>
+        <v>2815</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>0.12</v>
+        <v>2.58</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -11152,12 +11059,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -11176,13 +11083,13 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>2744.3</v>
+        <v>1384</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>2815</v>
-      </c>
-      <c r="I94" s="7" t="n">
-        <v>2.58</v>
+        <v>1369</v>
+      </c>
+      <c r="I94" s="8" t="n">
+        <v>-1.08</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -11213,12 +11120,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -11233,17 +11140,17 @@
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G95" s="6" t="n">
-        <v>1384</v>
+        <v>415.15</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>1369</v>
+        <v>411</v>
       </c>
       <c r="I95" s="8" t="n">
-        <v>-1.08</v>
+        <v>-1</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -11274,12 +11181,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -11298,13 +11205,13 @@
         </is>
       </c>
       <c r="G96" s="6" t="n">
-        <v>415.15</v>
+        <v>552.4</v>
       </c>
       <c r="H96" s="6" t="n">
-        <v>411</v>
-      </c>
-      <c r="I96" s="8" t="n">
-        <v>-1</v>
+        <v>595.15</v>
+      </c>
+      <c r="I96" s="7" t="n">
+        <v>7.74</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -11335,12 +11242,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -11355,17 +11262,17 @@
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G97" s="6" t="n">
-        <v>552.4</v>
+        <v>129.2</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>595.15</v>
-      </c>
-      <c r="I97" s="7" t="n">
-        <v>7.74</v>
+        <v>126.3</v>
+      </c>
+      <c r="I97" s="8" t="n">
+        <v>-2.24</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -11396,12 +11303,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -11420,13 +11327,13 @@
         </is>
       </c>
       <c r="G98" s="6" t="n">
-        <v>129.2</v>
+        <v>391.3</v>
       </c>
       <c r="H98" s="6" t="n">
-        <v>126.3</v>
-      </c>
-      <c r="I98" s="8" t="n">
-        <v>-2.24</v>
+        <v>393</v>
+      </c>
+      <c r="I98" s="7" t="n">
+        <v>0.43</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -12006,12 +11913,12 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -12030,13 +11937,13 @@
         </is>
       </c>
       <c r="G108" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H108" s="6" t="n">
-        <v>406</v>
+        <v>5536</v>
       </c>
       <c r="I108" s="7" t="n">
-        <v>3.76</v>
+        <v>0.67</v>
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
@@ -12067,12 +11974,12 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -12087,17 +11994,17 @@
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G109" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>5536</v>
+        <v>114.03</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
@@ -12128,12 +12035,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -12148,17 +12055,17 @@
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G110" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H110" s="6" t="n">
-        <v>114.03</v>
+        <v>2815</v>
       </c>
       <c r="I110" s="7" t="n">
-        <v>0.59</v>
+        <v>2.58</v>
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
@@ -12189,12 +12096,12 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -12213,13 +12120,13 @@
         </is>
       </c>
       <c r="G111" s="6" t="n">
-        <v>2744.3</v>
+        <v>1384</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>2815</v>
-      </c>
-      <c r="I111" s="7" t="n">
-        <v>2.58</v>
+        <v>1366</v>
+      </c>
+      <c r="I111" s="8" t="n">
+        <v>-1.3</v>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
@@ -12250,12 +12157,12 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -12270,17 +12177,17 @@
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G112" s="6" t="n">
-        <v>1384</v>
+        <v>415.15</v>
       </c>
       <c r="H112" s="6" t="n">
-        <v>1366</v>
+        <v>412.6</v>
       </c>
       <c r="I112" s="8" t="n">
-        <v>-1.3</v>
+        <v>-0.61</v>
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
@@ -12311,12 +12218,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -12335,13 +12242,13 @@
         </is>
       </c>
       <c r="G113" s="6" t="n">
-        <v>415.15</v>
+        <v>552.4</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>412.6</v>
-      </c>
-      <c r="I113" s="8" t="n">
-        <v>-0.61</v>
+        <v>586.65</v>
+      </c>
+      <c r="I113" s="7" t="n">
+        <v>6.2</v>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
@@ -12372,12 +12279,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -12392,17 +12299,17 @@
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G114" s="6" t="n">
-        <v>552.4</v>
+        <v>129.2</v>
       </c>
       <c r="H114" s="6" t="n">
-        <v>586.65</v>
-      </c>
-      <c r="I114" s="7" t="n">
-        <v>6.2</v>
+        <v>126.3</v>
+      </c>
+      <c r="I114" s="8" t="n">
+        <v>-2.24</v>
       </c>
       <c r="J114" s="6" t="inlineStr">
         <is>
@@ -12433,12 +12340,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -12457,13 +12364,13 @@
         </is>
       </c>
       <c r="G115" s="6" t="n">
-        <v>129.2</v>
+        <v>391.3</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>126.3</v>
-      </c>
-      <c r="I115" s="8" t="n">
-        <v>-2.24</v>
+        <v>406</v>
+      </c>
+      <c r="I115" s="7" t="n">
+        <v>3.76</v>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
@@ -13043,12 +12950,12 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -13067,13 +12974,13 @@
         </is>
       </c>
       <c r="G125" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>406</v>
+        <v>5536</v>
       </c>
       <c r="I125" s="7" t="n">
-        <v>3.76</v>
+        <v>0.67</v>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
@@ -13104,12 +13011,12 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -13124,17 +13031,17 @@
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G126" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H126" s="6" t="n">
-        <v>5536</v>
+        <v>114.03</v>
       </c>
       <c r="I126" s="7" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
@@ -13165,12 +13072,12 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -13185,17 +13092,17 @@
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G127" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>114.03</v>
+        <v>2780</v>
       </c>
       <c r="I127" s="7" t="n">
-        <v>0.59</v>
+        <v>1.3</v>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
@@ -13226,12 +13133,12 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -13250,13 +13157,13 @@
         </is>
       </c>
       <c r="G128" s="6" t="n">
-        <v>2744.3</v>
+        <v>1384</v>
       </c>
       <c r="H128" s="6" t="n">
-        <v>2780</v>
-      </c>
-      <c r="I128" s="7" t="n">
-        <v>1.3</v>
+        <v>1366</v>
+      </c>
+      <c r="I128" s="8" t="n">
+        <v>-1.3</v>
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
@@ -13287,12 +13194,12 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -13307,17 +13214,17 @@
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G129" s="6" t="n">
-        <v>1384</v>
+        <v>415.15</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>1366</v>
+        <v>412.6</v>
       </c>
       <c r="I129" s="8" t="n">
-        <v>-1.3</v>
+        <v>-0.61</v>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
@@ -13348,12 +13255,12 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -13372,13 +13279,13 @@
         </is>
       </c>
       <c r="G130" s="6" t="n">
-        <v>415.15</v>
+        <v>552.4</v>
       </c>
       <c r="H130" s="6" t="n">
-        <v>412.6</v>
-      </c>
-      <c r="I130" s="8" t="n">
-        <v>-0.61</v>
+        <v>586.65</v>
+      </c>
+      <c r="I130" s="7" t="n">
+        <v>6.2</v>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
@@ -13409,12 +13316,12 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
@@ -13429,17 +13336,17 @@
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G131" s="6" t="n">
-        <v>552.4</v>
+        <v>129.2</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>586.65</v>
-      </c>
-      <c r="I131" s="7" t="n">
-        <v>6.2</v>
+        <v>126</v>
+      </c>
+      <c r="I131" s="8" t="n">
+        <v>-2.48</v>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
@@ -13470,12 +13377,12 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -13494,13 +13401,13 @@
         </is>
       </c>
       <c r="G132" s="6" t="n">
-        <v>129.2</v>
+        <v>391.3</v>
       </c>
       <c r="H132" s="6" t="n">
-        <v>126</v>
-      </c>
-      <c r="I132" s="8" t="n">
-        <v>-2.48</v>
+        <v>406</v>
+      </c>
+      <c r="I132" s="7" t="n">
+        <v>3.76</v>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
@@ -14080,12 +13987,12 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -14104,13 +14011,13 @@
         </is>
       </c>
       <c r="G142" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H142" s="6" t="n">
-        <v>417</v>
-      </c>
-      <c r="I142" s="7" t="n">
-        <v>6.57</v>
+        <v>5474</v>
+      </c>
+      <c r="I142" s="8" t="n">
+        <v>-0.45</v>
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
@@ -14141,12 +14048,12 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
@@ -14161,17 +14068,17 @@
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G143" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H143" s="6" t="n">
-        <v>5474</v>
-      </c>
-      <c r="I143" s="8" t="n">
-        <v>-0.45</v>
+        <v>118.98</v>
+      </c>
+      <c r="I143" s="7" t="n">
+        <v>4.96</v>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
@@ -14202,12 +14109,12 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
@@ -14222,17 +14129,17 @@
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G144" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H144" s="6" t="n">
-        <v>118.98</v>
+        <v>2839</v>
       </c>
       <c r="I144" s="7" t="n">
-        <v>4.96</v>
+        <v>3.45</v>
       </c>
       <c r="J144" s="6" t="inlineStr">
         <is>
@@ -14263,12 +14170,12 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
@@ -14287,13 +14194,13 @@
         </is>
       </c>
       <c r="G145" s="6" t="n">
-        <v>2744.3</v>
+        <v>1384</v>
       </c>
       <c r="H145" s="6" t="n">
-        <v>2839</v>
-      </c>
-      <c r="I145" s="7" t="n">
-        <v>3.45</v>
+        <v>1332.3</v>
+      </c>
+      <c r="I145" s="8" t="n">
+        <v>-3.74</v>
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
@@ -14324,12 +14231,12 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
@@ -14344,17 +14251,17 @@
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G146" s="6" t="n">
-        <v>1384</v>
+        <v>415.15</v>
       </c>
       <c r="H146" s="6" t="n">
-        <v>1332.3</v>
+        <v>409.3</v>
       </c>
       <c r="I146" s="8" t="n">
-        <v>-3.74</v>
+        <v>-1.41</v>
       </c>
       <c r="J146" s="6" t="inlineStr">
         <is>
@@ -14385,12 +14292,12 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
@@ -14409,13 +14316,13 @@
         </is>
       </c>
       <c r="G147" s="6" t="n">
-        <v>415.15</v>
+        <v>552.4</v>
       </c>
       <c r="H147" s="6" t="n">
-        <v>409.3</v>
-      </c>
-      <c r="I147" s="8" t="n">
-        <v>-1.41</v>
+        <v>584.6</v>
+      </c>
+      <c r="I147" s="7" t="n">
+        <v>5.83</v>
       </c>
       <c r="J147" s="6" t="inlineStr">
         <is>
@@ -14446,12 +14353,12 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
@@ -14466,17 +14373,17 @@
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G148" s="6" t="n">
-        <v>552.4</v>
+        <v>129.2</v>
       </c>
       <c r="H148" s="6" t="n">
-        <v>584.6</v>
-      </c>
-      <c r="I148" s="7" t="n">
-        <v>5.83</v>
+        <v>125.95</v>
+      </c>
+      <c r="I148" s="8" t="n">
+        <v>-2.52</v>
       </c>
       <c r="J148" s="6" t="inlineStr">
         <is>
@@ -14507,12 +14414,12 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
@@ -14531,13 +14438,13 @@
         </is>
       </c>
       <c r="G149" s="6" t="n">
-        <v>129.2</v>
+        <v>391.3</v>
       </c>
       <c r="H149" s="6" t="n">
-        <v>125.95</v>
-      </c>
-      <c r="I149" s="8" t="n">
-        <v>-2.52</v>
+        <v>417</v>
+      </c>
+      <c r="I149" s="7" t="n">
+        <v>6.57</v>
       </c>
       <c r="J149" s="6" t="inlineStr">
         <is>
@@ -15117,12 +15024,12 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
@@ -15141,13 +15048,13 @@
         </is>
       </c>
       <c r="G159" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H159" s="6" t="n">
-        <v>413.5</v>
+        <v>5580</v>
       </c>
       <c r="I159" s="7" t="n">
-        <v>5.67</v>
+        <v>1.47</v>
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
@@ -15178,12 +15085,12 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
@@ -15198,17 +15105,17 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G160" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H160" s="6" t="n">
-        <v>5580</v>
+        <v>118</v>
       </c>
       <c r="I160" s="7" t="n">
-        <v>1.47</v>
+        <v>4.09</v>
       </c>
       <c r="J160" s="6" t="inlineStr">
         <is>
@@ -15239,12 +15146,12 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
@@ -15259,17 +15166,17 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G161" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H161" s="6" t="n">
-        <v>118</v>
-      </c>
-      <c r="I161" s="7" t="n">
-        <v>4.09</v>
+        <v>2733.5</v>
+      </c>
+      <c r="I161" s="8" t="n">
+        <v>-0.39</v>
       </c>
       <c r="J161" s="6" t="inlineStr">
         <is>
@@ -15300,12 +15207,12 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
@@ -15324,13 +15231,13 @@
         </is>
       </c>
       <c r="G162" s="6" t="n">
-        <v>2744.3</v>
+        <v>1384</v>
       </c>
       <c r="H162" s="6" t="n">
-        <v>2733.5</v>
+        <v>1348</v>
       </c>
       <c r="I162" s="8" t="n">
-        <v>-0.39</v>
+        <v>-2.6</v>
       </c>
       <c r="J162" s="6" t="inlineStr">
         <is>
@@ -15361,12 +15268,12 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
@@ -15381,17 +15288,17 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G163" s="6" t="n">
-        <v>1384</v>
+        <v>415.15</v>
       </c>
       <c r="H163" s="6" t="n">
-        <v>1348</v>
+        <v>407.1</v>
       </c>
       <c r="I163" s="8" t="n">
-        <v>-2.6</v>
+        <v>-1.94</v>
       </c>
       <c r="J163" s="6" t="inlineStr">
         <is>
@@ -15422,12 +15329,12 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
@@ -15446,13 +15353,13 @@
         </is>
       </c>
       <c r="G164" s="6" t="n">
-        <v>415.15</v>
+        <v>552.4</v>
       </c>
       <c r="H164" s="6" t="n">
-        <v>407.1</v>
-      </c>
-      <c r="I164" s="8" t="n">
-        <v>-1.94</v>
+        <v>561.9</v>
+      </c>
+      <c r="I164" s="7" t="n">
+        <v>1.72</v>
       </c>
       <c r="J164" s="6" t="inlineStr">
         <is>
@@ -15483,12 +15390,12 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
@@ -15503,17 +15410,17 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G165" s="6" t="n">
-        <v>552.4</v>
+        <v>129.2</v>
       </c>
       <c r="H165" s="6" t="n">
-        <v>561.9</v>
-      </c>
-      <c r="I165" s="7" t="n">
-        <v>1.72</v>
+        <v>124.75</v>
+      </c>
+      <c r="I165" s="8" t="n">
+        <v>-3.44</v>
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
@@ -15544,12 +15451,12 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
@@ -15568,13 +15475,13 @@
         </is>
       </c>
       <c r="G166" s="6" t="n">
-        <v>129.2</v>
+        <v>391.3</v>
       </c>
       <c r="H166" s="6" t="n">
-        <v>124.75</v>
-      </c>
-      <c r="I166" s="8" t="n">
-        <v>-3.44</v>
+        <v>413.5</v>
+      </c>
+      <c r="I166" s="7" t="n">
+        <v>5.67</v>
       </c>
       <c r="J166" s="6" t="inlineStr">
         <is>
@@ -16032,12 +15939,12 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
@@ -16056,13 +15963,13 @@
         </is>
       </c>
       <c r="G174" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H174" s="6" t="n">
-        <v>410</v>
+        <v>5570</v>
       </c>
       <c r="I174" s="7" t="n">
-        <v>4.78</v>
+        <v>1.29</v>
       </c>
       <c r="J174" s="6" t="inlineStr">
         <is>
@@ -16093,12 +16000,12 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
@@ -16113,17 +16020,17 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G175" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H175" s="6" t="n">
-        <v>5570</v>
+        <v>117.32</v>
       </c>
       <c r="I175" s="7" t="n">
-        <v>1.29</v>
+        <v>3.49</v>
       </c>
       <c r="J175" s="6" t="inlineStr">
         <is>
@@ -16154,12 +16061,12 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
@@ -16174,17 +16081,17 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G176" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H176" s="6" t="n">
-        <v>117.32</v>
-      </c>
-      <c r="I176" s="7" t="n">
-        <v>3.49</v>
+        <v>2741.3999</v>
+      </c>
+      <c r="I176" s="8" t="n">
+        <v>-0.11</v>
       </c>
       <c r="J176" s="6" t="inlineStr">
         <is>
@@ -16215,12 +16122,12 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
@@ -16235,17 +16142,17 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G177" s="6" t="n">
-        <v>2744.3</v>
+        <v>415.15</v>
       </c>
       <c r="H177" s="6" t="n">
-        <v>2741.3999</v>
+        <v>408.45</v>
       </c>
       <c r="I177" s="8" t="n">
-        <v>-0.11</v>
+        <v>-1.61</v>
       </c>
       <c r="J177" s="6" t="inlineStr">
         <is>
@@ -16276,12 +16183,12 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
@@ -16300,13 +16207,13 @@
         </is>
       </c>
       <c r="G178" s="6" t="n">
-        <v>415.15</v>
+        <v>552.4</v>
       </c>
       <c r="H178" s="6" t="n">
-        <v>408.45</v>
-      </c>
-      <c r="I178" s="8" t="n">
-        <v>-1.61</v>
+        <v>567.5</v>
+      </c>
+      <c r="I178" s="7" t="n">
+        <v>2.73</v>
       </c>
       <c r="J178" s="6" t="inlineStr">
         <is>
@@ -16337,12 +16244,12 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
@@ -16357,17 +16264,17 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G179" s="6" t="n">
-        <v>552.4</v>
+        <v>129.2</v>
       </c>
       <c r="H179" s="6" t="n">
-        <v>567.5</v>
-      </c>
-      <c r="I179" s="7" t="n">
-        <v>2.73</v>
+        <v>125.3</v>
+      </c>
+      <c r="I179" s="8" t="n">
+        <v>-3.02</v>
       </c>
       <c r="J179" s="6" t="inlineStr">
         <is>
@@ -16398,12 +16305,12 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
@@ -16422,13 +16329,13 @@
         </is>
       </c>
       <c r="G180" s="6" t="n">
-        <v>129.2</v>
+        <v>391.3</v>
       </c>
       <c r="H180" s="6" t="n">
-        <v>125.3</v>
-      </c>
-      <c r="I180" s="8" t="n">
-        <v>-3.02</v>
+        <v>410</v>
+      </c>
+      <c r="I180" s="7" t="n">
+        <v>4.78</v>
       </c>
       <c r="J180" s="6" t="inlineStr">
         <is>
@@ -16825,12 +16732,12 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
@@ -16849,13 +16756,13 @@
         </is>
       </c>
       <c r="G187" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H187" s="6" t="n">
-        <v>410</v>
-      </c>
-      <c r="I187" s="7" t="n">
-        <v>4.78</v>
+        <v>5442.5</v>
+      </c>
+      <c r="I187" s="8" t="n">
+        <v>-1.03</v>
       </c>
       <c r="J187" s="6" t="inlineStr">
         <is>
@@ -16886,12 +16793,12 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
@@ -16906,17 +16813,17 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G188" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H188" s="6" t="n">
-        <v>5442.5</v>
-      </c>
-      <c r="I188" s="8" t="n">
-        <v>-1.03</v>
+        <v>116.5</v>
+      </c>
+      <c r="I188" s="7" t="n">
+        <v>2.77</v>
       </c>
       <c r="J188" s="6" t="inlineStr">
         <is>
@@ -16947,12 +16854,12 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
@@ -16967,17 +16874,17 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G189" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H189" s="6" t="n">
-        <v>116.5</v>
+        <v>2959</v>
       </c>
       <c r="I189" s="7" t="n">
-        <v>2.77</v>
+        <v>7.82</v>
       </c>
       <c r="J189" s="6" t="inlineStr">
         <is>
@@ -17008,12 +16915,12 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
@@ -17028,17 +16935,17 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G190" s="6" t="n">
-        <v>2744.3</v>
+        <v>415.15</v>
       </c>
       <c r="H190" s="6" t="n">
-        <v>2959</v>
-      </c>
-      <c r="I190" s="7" t="n">
-        <v>7.82</v>
+        <v>406.9</v>
+      </c>
+      <c r="I190" s="8" t="n">
+        <v>-1.99</v>
       </c>
       <c r="J190" s="6" t="inlineStr">
         <is>
@@ -17069,12 +16976,12 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
@@ -17089,17 +16996,17 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G191" s="6" t="n">
-        <v>415.15</v>
+        <v>391.3</v>
       </c>
       <c r="H191" s="6" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="I191" s="8" t="n">
-        <v>-1.99</v>
+        <v>410</v>
+      </c>
+      <c r="I191" s="7" t="n">
+        <v>4.78</v>
       </c>
       <c r="J191" s="6" t="inlineStr">
         <is>
@@ -17496,12 +17403,12 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
@@ -17520,13 +17427,13 @@
         </is>
       </c>
       <c r="G198" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H198" s="6" t="n">
-        <v>413.1</v>
+        <v>5510</v>
       </c>
       <c r="I198" s="7" t="n">
-        <v>5.57</v>
+        <v>0.2</v>
       </c>
       <c r="J198" s="6" t="inlineStr">
         <is>
@@ -17557,12 +17464,12 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
@@ -17577,17 +17484,17 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G199" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H199" s="6" t="n">
-        <v>5510</v>
+        <v>117.48</v>
       </c>
       <c r="I199" s="7" t="n">
-        <v>0.2</v>
+        <v>3.63</v>
       </c>
       <c r="J199" s="6" t="inlineStr">
         <is>
@@ -17618,12 +17525,12 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
@@ -17638,17 +17545,17 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G200" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H200" s="6" t="n">
-        <v>117.48</v>
+        <v>2961</v>
       </c>
       <c r="I200" s="7" t="n">
-        <v>3.63</v>
+        <v>7.9</v>
       </c>
       <c r="J200" s="6" t="inlineStr">
         <is>
@@ -17679,12 +17586,12 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
@@ -17699,17 +17606,17 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G201" s="6" t="n">
-        <v>2744.3</v>
+        <v>415.15</v>
       </c>
       <c r="H201" s="6" t="n">
-        <v>2961</v>
-      </c>
-      <c r="I201" s="7" t="n">
-        <v>7.9</v>
+        <v>400</v>
+      </c>
+      <c r="I201" s="8" t="n">
+        <v>-3.65</v>
       </c>
       <c r="J201" s="6" t="inlineStr">
         <is>
@@ -17740,12 +17647,12 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
@@ -17760,17 +17667,17 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G202" s="6" t="n">
-        <v>415.15</v>
+        <v>391.3</v>
       </c>
       <c r="H202" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="I202" s="8" t="n">
-        <v>-3.65</v>
+        <v>413.1</v>
+      </c>
+      <c r="I202" s="7" t="n">
+        <v>5.57</v>
       </c>
       <c r="J202" s="6" t="inlineStr">
         <is>
@@ -18167,12 +18074,12 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
@@ -18191,13 +18098,13 @@
         </is>
       </c>
       <c r="G209" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H209" s="6" t="n">
-        <v>419</v>
+        <v>5674</v>
       </c>
       <c r="I209" s="7" t="n">
-        <v>7.08</v>
+        <v>3.18</v>
       </c>
       <c r="J209" s="6" t="inlineStr">
         <is>
@@ -18228,12 +18135,12 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
@@ -18248,17 +18155,17 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G210" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H210" s="6" t="n">
-        <v>5674</v>
+        <v>118</v>
       </c>
       <c r="I210" s="7" t="n">
-        <v>3.18</v>
+        <v>4.09</v>
       </c>
       <c r="J210" s="6" t="inlineStr">
         <is>
@@ -18289,12 +18196,12 @@
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
@@ -18309,17 +18216,17 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G211" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H211" s="6" t="n">
-        <v>118</v>
+        <v>2930</v>
       </c>
       <c r="I211" s="7" t="n">
-        <v>4.09</v>
+        <v>6.77</v>
       </c>
       <c r="J211" s="6" t="inlineStr">
         <is>
@@ -18350,12 +18257,12 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
@@ -18370,17 +18277,17 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G212" s="6" t="n">
-        <v>2744.3</v>
+        <v>415.15</v>
       </c>
       <c r="H212" s="6" t="n">
-        <v>2930</v>
-      </c>
-      <c r="I212" s="7" t="n">
-        <v>6.77</v>
+        <v>402.5</v>
+      </c>
+      <c r="I212" s="8" t="n">
+        <v>-3.05</v>
       </c>
       <c r="J212" s="6" t="inlineStr">
         <is>
@@ -18411,12 +18318,12 @@
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D213" s="6" t="inlineStr">
@@ -18431,17 +18338,17 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G213" s="6" t="n">
-        <v>415.15</v>
+        <v>391.3</v>
       </c>
       <c r="H213" s="6" t="n">
-        <v>402.5</v>
-      </c>
-      <c r="I213" s="8" t="n">
-        <v>-3.05</v>
+        <v>419</v>
+      </c>
+      <c r="I213" s="7" t="n">
+        <v>7.08</v>
       </c>
       <c r="J213" s="6" t="inlineStr">
         <is>
@@ -18838,12 +18745,12 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D220" s="6" t="inlineStr">
@@ -18862,13 +18769,13 @@
         </is>
       </c>
       <c r="G220" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H220" s="6" t="n">
-        <v>422.25</v>
+        <v>5667.5</v>
       </c>
       <c r="I220" s="7" t="n">
-        <v>7.91</v>
+        <v>3.06</v>
       </c>
       <c r="J220" s="6" t="inlineStr">
         <is>
@@ -18899,12 +18806,12 @@
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D221" s="6" t="inlineStr">
@@ -18919,17 +18826,17 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G221" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H221" s="6" t="n">
-        <v>5667.5</v>
+        <v>116.55</v>
       </c>
       <c r="I221" s="7" t="n">
-        <v>3.06</v>
+        <v>2.81</v>
       </c>
       <c r="J221" s="6" t="inlineStr">
         <is>
@@ -18960,12 +18867,12 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D222" s="6" t="inlineStr">
@@ -18980,17 +18887,17 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G222" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H222" s="6" t="n">
-        <v>116.55</v>
+        <v>2885.8</v>
       </c>
       <c r="I222" s="7" t="n">
-        <v>2.81</v>
+        <v>5.16</v>
       </c>
       <c r="J222" s="6" t="inlineStr">
         <is>
@@ -19021,12 +18928,12 @@
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D223" s="6" t="inlineStr">
@@ -19041,17 +18948,17 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G223" s="6" t="n">
-        <v>2744.3</v>
+        <v>415.15</v>
       </c>
       <c r="H223" s="6" t="n">
-        <v>2885.8</v>
-      </c>
-      <c r="I223" s="7" t="n">
-        <v>5.16</v>
+        <v>405.2</v>
+      </c>
+      <c r="I223" s="8" t="n">
+        <v>-2.4</v>
       </c>
       <c r="J223" s="6" t="inlineStr">
         <is>
@@ -19082,12 +18989,12 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D224" s="6" t="inlineStr">
@@ -19102,17 +19009,17 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G224" s="6" t="n">
-        <v>415.15</v>
+        <v>391.3</v>
       </c>
       <c r="H224" s="6" t="n">
-        <v>405.2</v>
-      </c>
-      <c r="I224" s="8" t="n">
-        <v>-2.4</v>
+        <v>422.25</v>
+      </c>
+      <c r="I224" s="7" t="n">
+        <v>7.91</v>
       </c>
       <c r="J224" s="6" t="inlineStr">
         <is>
@@ -19509,12 +19416,12 @@
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D231" s="6" t="inlineStr">
@@ -19533,13 +19440,13 @@
         </is>
       </c>
       <c r="G231" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H231" s="6" t="n">
-        <v>426</v>
+        <v>5693.5</v>
       </c>
       <c r="I231" s="7" t="n">
-        <v>8.869999999999999</v>
+        <v>3.54</v>
       </c>
       <c r="J231" s="6" t="inlineStr">
         <is>
@@ -19570,12 +19477,12 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D232" s="6" t="inlineStr">
@@ -19590,17 +19497,17 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G232" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H232" s="6" t="n">
-        <v>5693.5</v>
+        <v>116.5</v>
       </c>
       <c r="I232" s="7" t="n">
-        <v>3.54</v>
+        <v>2.77</v>
       </c>
       <c r="J232" s="6" t="inlineStr">
         <is>
@@ -19631,12 +19538,12 @@
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
@@ -19651,17 +19558,17 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G233" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H233" s="6" t="n">
-        <v>116.5</v>
+        <v>2875.8</v>
       </c>
       <c r="I233" s="7" t="n">
-        <v>2.77</v>
+        <v>4.79</v>
       </c>
       <c r="J233" s="6" t="inlineStr">
         <is>
@@ -19692,12 +19599,12 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C234" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D234" s="6" t="inlineStr">
@@ -19712,17 +19619,17 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G234" s="6" t="n">
-        <v>2744.3</v>
+        <v>415.15</v>
       </c>
       <c r="H234" s="6" t="n">
-        <v>2875.8</v>
-      </c>
-      <c r="I234" s="7" t="n">
-        <v>4.79</v>
+        <v>406</v>
+      </c>
+      <c r="I234" s="8" t="n">
+        <v>-2.2</v>
       </c>
       <c r="J234" s="6" t="inlineStr">
         <is>
@@ -19753,12 +19660,12 @@
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D235" s="6" t="inlineStr">
@@ -19773,17 +19680,17 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G235" s="6" t="n">
-        <v>415.15</v>
+        <v>391.3</v>
       </c>
       <c r="H235" s="6" t="n">
-        <v>406</v>
-      </c>
-      <c r="I235" s="8" t="n">
-        <v>-2.2</v>
+        <v>426</v>
+      </c>
+      <c r="I235" s="7" t="n">
+        <v>8.869999999999999</v>
       </c>
       <c r="J235" s="6" t="inlineStr">
         <is>
@@ -20180,12 +20087,12 @@
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D242" s="6" t="inlineStr">
@@ -20204,13 +20111,13 @@
         </is>
       </c>
       <c r="G242" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H242" s="6" t="n">
-        <v>425.65</v>
+        <v>5616</v>
       </c>
       <c r="I242" s="7" t="n">
-        <v>8.779999999999999</v>
+        <v>2.13</v>
       </c>
       <c r="J242" s="6" t="inlineStr">
         <is>
@@ -20241,12 +20148,12 @@
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D243" s="6" t="inlineStr">
@@ -20261,17 +20168,17 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G243" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H243" s="6" t="n">
-        <v>5616</v>
+        <v>115.79</v>
       </c>
       <c r="I243" s="7" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="J243" s="6" t="inlineStr">
         <is>
@@ -20302,12 +20209,12 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C244" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D244" s="6" t="inlineStr">
@@ -20322,17 +20229,17 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G244" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H244" s="6" t="n">
-        <v>115.79</v>
+        <v>2852.2</v>
       </c>
       <c r="I244" s="7" t="n">
-        <v>2.14</v>
+        <v>3.93</v>
       </c>
       <c r="J244" s="6" t="inlineStr">
         <is>
@@ -20363,12 +20270,12 @@
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D245" s="6" t="inlineStr">
@@ -20383,17 +20290,17 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G245" s="6" t="n">
-        <v>2744.3</v>
+        <v>415.15</v>
       </c>
       <c r="H245" s="6" t="n">
-        <v>2852.2</v>
-      </c>
-      <c r="I245" s="7" t="n">
-        <v>3.93</v>
+        <v>405.8</v>
+      </c>
+      <c r="I245" s="8" t="n">
+        <v>-2.25</v>
       </c>
       <c r="J245" s="6" t="inlineStr">
         <is>
@@ -20424,12 +20331,12 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C246" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D246" s="6" t="inlineStr">
@@ -20444,17 +20351,17 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G246" s="6" t="n">
-        <v>415.15</v>
+        <v>391.3</v>
       </c>
       <c r="H246" s="6" t="n">
-        <v>405.8</v>
-      </c>
-      <c r="I246" s="8" t="n">
-        <v>-2.25</v>
+        <v>425.65</v>
+      </c>
+      <c r="I246" s="7" t="n">
+        <v>8.779999999999999</v>
       </c>
       <c r="J246" s="6" t="inlineStr">
         <is>
@@ -20851,12 +20758,12 @@
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D253" s="6" t="inlineStr">
@@ -20875,13 +20782,13 @@
         </is>
       </c>
       <c r="G253" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H253" s="6" t="n">
-        <v>424</v>
+        <v>5655</v>
       </c>
       <c r="I253" s="7" t="n">
-        <v>8.359999999999999</v>
+        <v>2.84</v>
       </c>
       <c r="J253" s="6" t="inlineStr">
         <is>
@@ -20912,12 +20819,12 @@
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C254" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D254" s="6" t="inlineStr">
@@ -20932,17 +20839,17 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G254" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H254" s="6" t="n">
-        <v>5655</v>
+        <v>115.93</v>
       </c>
       <c r="I254" s="7" t="n">
-        <v>2.84</v>
+        <v>2.27</v>
       </c>
       <c r="J254" s="6" t="inlineStr">
         <is>
@@ -20973,12 +20880,12 @@
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D255" s="6" t="inlineStr">
@@ -20993,17 +20900,17 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G255" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H255" s="6" t="n">
-        <v>115.93</v>
+        <v>2888</v>
       </c>
       <c r="I255" s="7" t="n">
-        <v>2.27</v>
+        <v>5.24</v>
       </c>
       <c r="J255" s="6" t="inlineStr">
         <is>
@@ -21034,12 +20941,12 @@
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C256" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D256" s="6" t="inlineStr">
@@ -21054,17 +20961,17 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G256" s="6" t="n">
-        <v>2744.3</v>
+        <v>415.15</v>
       </c>
       <c r="H256" s="6" t="n">
-        <v>2888</v>
-      </c>
-      <c r="I256" s="7" t="n">
-        <v>5.24</v>
+        <v>404</v>
+      </c>
+      <c r="I256" s="8" t="n">
+        <v>-2.69</v>
       </c>
       <c r="J256" s="6" t="inlineStr">
         <is>
@@ -21095,12 +21002,12 @@
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D257" s="6" t="inlineStr">
@@ -21115,17 +21022,17 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G257" s="6" t="n">
-        <v>415.15</v>
+        <v>391.3</v>
       </c>
       <c r="H257" s="6" t="n">
-        <v>404</v>
-      </c>
-      <c r="I257" s="8" t="n">
-        <v>-2.69</v>
+        <v>424</v>
+      </c>
+      <c r="I257" s="7" t="n">
+        <v>8.359999999999999</v>
       </c>
       <c r="J257" s="6" t="inlineStr">
         <is>
@@ -21522,12 +21429,12 @@
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C264" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D264" s="6" t="inlineStr">
@@ -21546,13 +21453,13 @@
         </is>
       </c>
       <c r="G264" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H264" s="6" t="n">
-        <v>413.95</v>
+        <v>5655</v>
       </c>
       <c r="I264" s="7" t="n">
-        <v>5.79</v>
+        <v>2.84</v>
       </c>
       <c r="J264" s="6" t="inlineStr">
         <is>
@@ -21583,12 +21490,12 @@
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C265" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D265" s="6" t="inlineStr">
@@ -21603,17 +21510,17 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G265" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H265" s="6" t="n">
-        <v>5655</v>
+        <v>115.4</v>
       </c>
       <c r="I265" s="7" t="n">
-        <v>2.84</v>
+        <v>1.8</v>
       </c>
       <c r="J265" s="6" t="inlineStr">
         <is>
@@ -21644,12 +21551,12 @@
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C266" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D266" s="6" t="inlineStr">
@@ -21664,17 +21571,17 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G266" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H266" s="6" t="n">
-        <v>115.4</v>
+        <v>2870</v>
       </c>
       <c r="I266" s="7" t="n">
-        <v>1.8</v>
+        <v>4.58</v>
       </c>
       <c r="J266" s="6" t="inlineStr">
         <is>
@@ -21705,12 +21612,12 @@
       </c>
       <c r="B267" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D267" s="6" t="inlineStr">
@@ -21725,17 +21632,17 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G267" s="6" t="n">
-        <v>2744.3</v>
+        <v>415.15</v>
       </c>
       <c r="H267" s="6" t="n">
-        <v>2870</v>
-      </c>
-      <c r="I267" s="7" t="n">
-        <v>4.58</v>
+        <v>400</v>
+      </c>
+      <c r="I267" s="8" t="n">
+        <v>-3.65</v>
       </c>
       <c r="J267" s="6" t="inlineStr">
         <is>
@@ -21766,12 +21673,12 @@
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C268" s="6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D268" s="6" t="inlineStr">
@@ -21786,17 +21693,17 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G268" s="6" t="n">
-        <v>415.15</v>
+        <v>391.3</v>
       </c>
       <c r="H268" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="I268" s="8" t="n">
-        <v>-3.65</v>
+        <v>413.95</v>
+      </c>
+      <c r="I268" s="7" t="n">
+        <v>5.79</v>
       </c>
       <c r="J268" s="6" t="inlineStr">
         <is>
@@ -22193,12 +22100,12 @@
       </c>
       <c r="B275" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D275" s="6" t="inlineStr">
@@ -22217,13 +22124,13 @@
         </is>
       </c>
       <c r="G275" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H275" s="6" t="n">
-        <v>411.4</v>
+        <v>5791.5</v>
       </c>
       <c r="I275" s="7" t="n">
-        <v>5.14</v>
+        <v>5.32</v>
       </c>
       <c r="J275" s="6" t="inlineStr">
         <is>
@@ -22254,12 +22161,12 @@
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C276" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D276" s="6" t="inlineStr">
@@ -22274,17 +22181,17 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G276" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H276" s="6" t="n">
-        <v>5791.5</v>
+        <v>115.2</v>
       </c>
       <c r="I276" s="7" t="n">
-        <v>5.32</v>
+        <v>1.62</v>
       </c>
       <c r="J276" s="6" t="inlineStr">
         <is>
@@ -22315,12 +22222,12 @@
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C277" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D277" s="6" t="inlineStr">
@@ -22335,17 +22242,17 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G277" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H277" s="6" t="n">
-        <v>115.2</v>
+        <v>2852</v>
       </c>
       <c r="I277" s="7" t="n">
-        <v>1.62</v>
+        <v>3.92</v>
       </c>
       <c r="J277" s="6" t="inlineStr">
         <is>
@@ -22376,12 +22283,12 @@
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C278" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D278" s="6" t="inlineStr">
@@ -22400,13 +22307,13 @@
         </is>
       </c>
       <c r="G278" s="6" t="n">
-        <v>2744.3</v>
+        <v>391.3</v>
       </c>
       <c r="H278" s="6" t="n">
-        <v>2852</v>
+        <v>411.4</v>
       </c>
       <c r="I278" s="7" t="n">
-        <v>3.92</v>
+        <v>5.14</v>
       </c>
       <c r="J278" s="6" t="inlineStr">
         <is>
@@ -22803,12 +22710,12 @@
       </c>
       <c r="B285" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C285" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D285" s="6" t="inlineStr">
@@ -22827,13 +22734,13 @@
         </is>
       </c>
       <c r="G285" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H285" s="6" t="n">
-        <v>413.95</v>
+        <v>5625.5</v>
       </c>
       <c r="I285" s="7" t="n">
-        <v>5.79</v>
+        <v>2.3</v>
       </c>
       <c r="J285" s="6" t="inlineStr">
         <is>
@@ -22864,12 +22771,12 @@
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C286" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D286" s="6" t="inlineStr">
@@ -22884,17 +22791,17 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G286" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H286" s="6" t="n">
-        <v>5625.5</v>
-      </c>
-      <c r="I286" s="7" t="n">
-        <v>2.3</v>
+        <v>113.33</v>
+      </c>
+      <c r="I286" s="8" t="n">
+        <v>-0.03</v>
       </c>
       <c r="J286" s="6" t="inlineStr">
         <is>
@@ -22925,12 +22832,12 @@
       </c>
       <c r="B287" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D287" s="6" t="inlineStr">
@@ -22945,17 +22852,17 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G287" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H287" s="6" t="n">
-        <v>113.33</v>
-      </c>
-      <c r="I287" s="8" t="n">
-        <v>-0.03</v>
+        <v>2775.8999</v>
+      </c>
+      <c r="I287" s="7" t="n">
+        <v>1.15</v>
       </c>
       <c r="J287" s="6" t="inlineStr">
         <is>
@@ -22986,12 +22893,12 @@
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C288" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D288" s="6" t="inlineStr">
@@ -23010,13 +22917,13 @@
         </is>
       </c>
       <c r="G288" s="6" t="n">
-        <v>2744.3</v>
+        <v>391.3</v>
       </c>
       <c r="H288" s="6" t="n">
-        <v>2775.8999</v>
+        <v>413.95</v>
       </c>
       <c r="I288" s="7" t="n">
-        <v>1.15</v>
+        <v>5.79</v>
       </c>
       <c r="J288" s="6" t="inlineStr">
         <is>
@@ -23352,12 +23259,12 @@
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C294" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D294" s="6" t="inlineStr">
@@ -23376,13 +23283,13 @@
         </is>
       </c>
       <c r="G294" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H294" s="6" t="n">
-        <v>412.15</v>
+        <v>5800</v>
       </c>
       <c r="I294" s="7" t="n">
-        <v>5.33</v>
+        <v>5.47</v>
       </c>
       <c r="J294" s="6" t="inlineStr">
         <is>
@@ -23413,12 +23320,12 @@
       </c>
       <c r="B295" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C295" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D295" s="6" t="inlineStr">
@@ -23433,17 +23340,17 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G295" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H295" s="6" t="n">
-        <v>5800</v>
+        <v>115.22</v>
       </c>
       <c r="I295" s="7" t="n">
-        <v>5.47</v>
+        <v>1.64</v>
       </c>
       <c r="J295" s="6" t="inlineStr">
         <is>
@@ -23474,12 +23381,12 @@
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C296" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D296" s="6" t="inlineStr">
@@ -23494,17 +23401,17 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G296" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H296" s="6" t="n">
-        <v>115.22</v>
+        <v>2763.2</v>
       </c>
       <c r="I296" s="7" t="n">
-        <v>1.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J296" s="6" t="inlineStr">
         <is>
@@ -23535,12 +23442,12 @@
       </c>
       <c r="B297" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C297" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D297" s="6" t="inlineStr">
@@ -23559,13 +23466,13 @@
         </is>
       </c>
       <c r="G297" s="6" t="n">
-        <v>2744.3</v>
+        <v>391.3</v>
       </c>
       <c r="H297" s="6" t="n">
-        <v>2763.2</v>
+        <v>412.15</v>
       </c>
       <c r="I297" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>5.33</v>
       </c>
       <c r="J297" s="6" t="inlineStr">
         <is>
@@ -23623,10 +23530,10 @@
         <v>11475</v>
       </c>
       <c r="H298" s="6" t="n">
-        <v>11310</v>
+        <v>11100</v>
       </c>
       <c r="I298" s="8" t="n">
-        <v>-1.44</v>
+        <v>-3.27</v>
       </c>
       <c r="J298" s="6" t="inlineStr">
         <is>
@@ -23745,10 +23652,10 @@
         <v>452.35</v>
       </c>
       <c r="H300" s="6" t="n">
-        <v>412.3</v>
+        <v>411.45</v>
       </c>
       <c r="I300" s="8" t="n">
-        <v>-8.85</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="J300" s="6" t="inlineStr">
         <is>
@@ -23901,12 +23808,12 @@
       </c>
       <c r="B303" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C303" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D303" s="6" t="inlineStr">
@@ -23925,13 +23832,13 @@
         </is>
       </c>
       <c r="G303" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H303" s="6" t="n">
-        <v>408.25</v>
+        <v>5690</v>
       </c>
       <c r="I303" s="7" t="n">
-        <v>4.33</v>
+        <v>3.47</v>
       </c>
       <c r="J303" s="6" t="inlineStr">
         <is>
@@ -23962,12 +23869,12 @@
       </c>
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C304" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D304" s="6" t="inlineStr">
@@ -23982,17 +23889,17 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G304" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H304" s="6" t="n">
-        <v>5690</v>
+        <v>117</v>
       </c>
       <c r="I304" s="7" t="n">
-        <v>3.47</v>
+        <v>3.21</v>
       </c>
       <c r="J304" s="6" t="inlineStr">
         <is>
@@ -24023,12 +23930,12 @@
       </c>
       <c r="B305" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C305" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D305" s="6" t="inlineStr">
@@ -24043,17 +23950,17 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G305" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H305" s="6" t="n">
-        <v>117</v>
-      </c>
-      <c r="I305" s="7" t="n">
-        <v>3.21</v>
+        <v>2720</v>
+      </c>
+      <c r="I305" s="8" t="n">
+        <v>-0.89</v>
       </c>
       <c r="J305" s="6" t="inlineStr">
         <is>
@@ -24084,12 +23991,12 @@
       </c>
       <c r="B306" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C306" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D306" s="6" t="inlineStr">
@@ -24108,13 +24015,13 @@
         </is>
       </c>
       <c r="G306" s="6" t="n">
-        <v>2744.3</v>
+        <v>391.3</v>
       </c>
       <c r="H306" s="6" t="n">
-        <v>2720</v>
-      </c>
-      <c r="I306" s="8" t="n">
-        <v>-0.89</v>
+        <v>408.25</v>
+      </c>
+      <c r="I306" s="7" t="n">
+        <v>4.33</v>
       </c>
       <c r="J306" s="6" t="inlineStr">
         <is>
@@ -24172,10 +24079,10 @@
         <v>11475</v>
       </c>
       <c r="H307" s="6" t="n">
-        <v>11310</v>
+        <v>11100</v>
       </c>
       <c r="I307" s="8" t="n">
-        <v>-1.44</v>
+        <v>-3.27</v>
       </c>
       <c r="J307" s="6" t="inlineStr">
         <is>
@@ -24233,10 +24140,10 @@
         <v>709</v>
       </c>
       <c r="H308" s="6" t="n">
-        <v>670.45</v>
+        <v>677.4</v>
       </c>
       <c r="I308" s="8" t="n">
-        <v>-5.44</v>
+        <v>-4.46</v>
       </c>
       <c r="J308" s="6" t="inlineStr">
         <is>
@@ -24294,10 +24201,10 @@
         <v>452.35</v>
       </c>
       <c r="H309" s="6" t="n">
-        <v>412.3</v>
+        <v>418.3</v>
       </c>
       <c r="I309" s="8" t="n">
-        <v>-8.85</v>
+        <v>-7.53</v>
       </c>
       <c r="J309" s="6" t="inlineStr">
         <is>
@@ -24355,10 +24262,10 @@
         <v>553.3</v>
       </c>
       <c r="H310" s="6" t="n">
-        <v>576.95</v>
+        <v>587.35</v>
       </c>
       <c r="I310" s="7" t="n">
-        <v>4.27</v>
+        <v>6.15</v>
       </c>
       <c r="J310" s="6" t="inlineStr">
         <is>
@@ -24416,10 +24323,10 @@
         <v>284.85</v>
       </c>
       <c r="H311" s="6" t="n">
-        <v>266.3</v>
+        <v>263</v>
       </c>
       <c r="I311" s="8" t="n">
-        <v>-6.51</v>
+        <v>-7.67</v>
       </c>
       <c r="J311" s="6" t="inlineStr">
         <is>
@@ -24450,12 +24357,12 @@
       </c>
       <c r="B312" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C312" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D312" s="6" t="inlineStr">
@@ -24474,13 +24381,13 @@
         </is>
       </c>
       <c r="G312" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H312" s="6" t="n">
-        <v>408.25</v>
+        <v>5657</v>
       </c>
       <c r="I312" s="7" t="n">
-        <v>4.33</v>
+        <v>2.87</v>
       </c>
       <c r="J312" s="6" t="inlineStr">
         <is>
@@ -24511,12 +24418,12 @@
       </c>
       <c r="B313" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C313" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D313" s="6" t="inlineStr">
@@ -24531,17 +24438,17 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G313" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H313" s="6" t="n">
-        <v>5690</v>
+        <v>116.32</v>
       </c>
       <c r="I313" s="7" t="n">
-        <v>3.47</v>
+        <v>2.61</v>
       </c>
       <c r="J313" s="6" t="inlineStr">
         <is>
@@ -24572,12 +24479,12 @@
       </c>
       <c r="B314" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C314" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D314" s="6" t="inlineStr">
@@ -24592,17 +24499,17 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G314" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H314" s="6" t="n">
-        <v>117</v>
-      </c>
-      <c r="I314" s="7" t="n">
-        <v>3.21</v>
+        <v>2735.3999</v>
+      </c>
+      <c r="I314" s="8" t="n">
+        <v>-0.32</v>
       </c>
       <c r="J314" s="6" t="inlineStr">
         <is>
@@ -24633,12 +24540,12 @@
       </c>
       <c r="B315" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-LICI-20260805-035a2d</t>
         </is>
       </c>
       <c r="C315" s="6" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D315" s="6" t="inlineStr">
@@ -24657,13 +24564,13 @@
         </is>
       </c>
       <c r="G315" s="6" t="n">
-        <v>2744.3</v>
+        <v>391.3</v>
       </c>
       <c r="H315" s="6" t="n">
-        <v>2720</v>
-      </c>
-      <c r="I315" s="8" t="n">
-        <v>-0.89</v>
+        <v>416.9</v>
+      </c>
+      <c r="I315" s="7" t="n">
+        <v>6.54</v>
       </c>
       <c r="J315" s="6" t="inlineStr">
         <is>
@@ -24721,10 +24628,10 @@
         <v>11475</v>
       </c>
       <c r="H316" s="6" t="n">
-        <v>11310</v>
+        <v>11100</v>
       </c>
       <c r="I316" s="8" t="n">
-        <v>-1.44</v>
+        <v>-3.27</v>
       </c>
       <c r="J316" s="6" t="inlineStr">
         <is>
@@ -24782,10 +24689,10 @@
         <v>709</v>
       </c>
       <c r="H317" s="6" t="n">
-        <v>670.45</v>
+        <v>677.4</v>
       </c>
       <c r="I317" s="8" t="n">
-        <v>-5.44</v>
+        <v>-4.46</v>
       </c>
       <c r="J317" s="6" t="inlineStr">
         <is>
@@ -24843,10 +24750,10 @@
         <v>452.35</v>
       </c>
       <c r="H318" s="6" t="n">
-        <v>412.3</v>
+        <v>418.3</v>
       </c>
       <c r="I318" s="8" t="n">
-        <v>-8.85</v>
+        <v>-7.53</v>
       </c>
       <c r="J318" s="6" t="inlineStr">
         <is>
@@ -24904,10 +24811,10 @@
         <v>553.3</v>
       </c>
       <c r="H319" s="6" t="n">
-        <v>576.95</v>
+        <v>587.35</v>
       </c>
       <c r="I319" s="7" t="n">
-        <v>4.27</v>
+        <v>6.15</v>
       </c>
       <c r="J319" s="6" t="inlineStr">
         <is>
@@ -24965,10 +24872,10 @@
         <v>284.85</v>
       </c>
       <c r="H320" s="6" t="n">
-        <v>266.3</v>
+        <v>263</v>
       </c>
       <c r="I320" s="8" t="n">
-        <v>-6.51</v>
+        <v>-7.67</v>
       </c>
       <c r="J320" s="6" t="inlineStr">
         <is>
@@ -24999,12 +24906,12 @@
       </c>
       <c r="B321" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-LICI-20260805-035a2d</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="C321" s="6" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D321" s="6" t="inlineStr">
@@ -25023,13 +24930,13 @@
         </is>
       </c>
       <c r="G321" s="6" t="n">
-        <v>391.3</v>
+        <v>5499</v>
       </c>
       <c r="H321" s="6" t="n">
-        <v>408.25</v>
+        <v>5657</v>
       </c>
       <c r="I321" s="7" t="n">
-        <v>4.33</v>
+        <v>2.87</v>
       </c>
       <c r="J321" s="6" t="inlineStr">
         <is>
@@ -25060,12 +24967,12 @@
       </c>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="C322" s="6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D322" s="6" t="inlineStr">
@@ -25080,17 +24987,17 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G322" s="6" t="n">
-        <v>5499</v>
+        <v>113.36</v>
       </c>
       <c r="H322" s="6" t="n">
-        <v>5690</v>
+        <v>116.32</v>
       </c>
       <c r="I322" s="7" t="n">
-        <v>3.47</v>
+        <v>2.61</v>
       </c>
       <c r="J322" s="6" t="inlineStr">
         <is>
@@ -25121,12 +25028,12 @@
       </c>
       <c r="B323" s="6" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="C323" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D323" s="6" t="inlineStr">
@@ -25141,17 +25048,17 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G323" s="6" t="n">
-        <v>113.36</v>
+        <v>2744.3</v>
       </c>
       <c r="H323" s="6" t="n">
-        <v>117</v>
-      </c>
-      <c r="I323" s="7" t="n">
-        <v>3.21</v>
+        <v>2735.3999</v>
+      </c>
+      <c r="I323" s="8" t="n">
+        <v>-0.32</v>
       </c>
       <c r="J323" s="6" t="inlineStr">
         <is>
@@ -25174,97 +25081,36 @@
         </is>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B324" s="6" t="inlineStr">
-        <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
-        </is>
-      </c>
-      <c r="C324" s="6" t="inlineStr">
-        <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="D324" s="6" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E324" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="F324" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G324" s="6" t="n">
-        <v>2744.3</v>
-      </c>
-      <c r="H324" s="6" t="n">
-        <v>2720</v>
-      </c>
-      <c r="I324" s="8" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="J324" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K324" s="6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE · no canonical stop</t>
-        </is>
-      </c>
-      <c r="L324" s="6" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="M324" s="6" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
+    <row r="326">
+      <c r="A326" s="4" t="inlineStr">
+        <is>
+          <t>Reconstructed daily active-portfolio history from canonical Registry.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>Reconstructed daily active-portfolio history from canonical Registry.</t>
+          <t>One row per position per trading day while the position was genuinely active.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>One row per position per trading day while the position was genuinely active.</t>
+          <t>Excludes same-day administrative Registry records (entry_date == exit_date).</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>Excludes same-day administrative Registry records (entry_date == exit_date).</t>
+          <t>Dynamic Stop is populated ONLY for the current as-of date · historical dynamic stops are UNAVAILABLE because dynamic_risk_v2 stores only the current snapshot.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
-        <is>
-          <t>Dynamic Stop is populated ONLY for the current as-of date · historical dynamic stops are UNAVAILABLE because dynamic_risk_v2 stores only the current snapshot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="4" t="inlineStr">
         <is>
           <t>Never fabricated · UNAVAILABLE means the canonical source has no value for that day.</t>
         </is>
@@ -25273,12 +25119,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A330:M330"/>
+    <mergeCell ref="A326:M326"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A329:M329"/>
     <mergeCell ref="A328:M328"/>
     <mergeCell ref="A327:M327"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A331:M331"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25368,12 +25214,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1389 - 1464</t>
+          <t>1393 - 1467</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.2%) • outperforming Nifty • sector strength 71/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.4%) • outperforming Nifty • sector strength 85/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -25409,12 +25255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1881 - 1982</t>
+          <t>1866 - 1966</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty • sector strength 79/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+6.4%) • outperforming Nifty • sector strength 69/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -25442,7 +25288,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -25450,12 +25296,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>322 - 338</t>
+          <t>323 - 339</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-7.6%) • sector strength 36/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.4%) • sector strength 8/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -25473,12 +25319,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -25491,12 +25337,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>989 - 1053</t>
+          <t>397 - 420</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.7%) • outperforming Nifty • sector strength 71/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.5%) • sector strength 77/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -25532,12 +25378,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>261 - 273</t>
+          <t>259 - 272</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.2%) • sector strength 36/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.6%) • sector strength 8/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -25555,12 +25401,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -25573,12 +25419,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>394 - 418</t>
+          <t>229 - 243</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.2%) • sector strength 64/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.4%) • sector strength 54/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -25596,17 +25442,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -25614,12 +25460,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>230 - 245</t>
+          <t>408 - 432</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.8%) • sector strength 57/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.0%) • sector strength 38/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -25655,12 +25501,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>260 - 273</t>
+          <t>257 - 269</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.2%) • sector strength 29/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.1%) • sector strength 23/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -25678,7 +25524,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -25696,12 +25542,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>406 - 430</t>
+          <t>179 - 190</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.5%) • sector strength 21/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.2%) • sector strength 38/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -25719,12 +25565,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -25737,12 +25583,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>178 - 190</t>
+          <t>369 - 393</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.4%) • sector strength 21/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.6%) • sector strength 23/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -25778,12 +25624,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>459 - 486</t>
+          <t>461 - 488</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-17.1%) • sector strength 7/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION de</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.6%) • sector strength 15/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION d</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">

--- a/reports/telegram/aegis_india_2026-09-04.xlsx
+++ b/reports/telegram/aegis_india_2026-09-04.xlsx
@@ -2493,7 +2493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2887,6 +2887,83 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>230 files · newest mtime 0d ago</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fundamentals PIT freshness</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>trading_age=1d · unique_asof=1 (≥60 needed for F01-05 OOS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fundamentals substrate maturity</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Substrate-before-sophistication rule · F01-05 OOS unblock at 60 asof-dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WORKED_LEGACY remediation queue</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>19 schedulable · 7 blocked by substrate rule</t>
         </is>
       </c>
     </row>
